--- a/output/yearly_population_iteration_52_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_52_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5642</v>
+        <v>5505</v>
       </c>
       <c r="C2" t="n">
-        <v>13789</v>
+        <v>8416</v>
       </c>
       <c r="D2" t="n">
-        <v>37338</v>
+        <v>40522</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3683</v>
+        <v>4030</v>
       </c>
       <c r="C3" t="n">
-        <v>7319</v>
+        <v>5429</v>
       </c>
       <c r="D3" t="n">
-        <v>13798</v>
+        <v>21166</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2777</v>
+        <v>2842</v>
       </c>
       <c r="C4" t="n">
-        <v>7188</v>
+        <v>5849</v>
       </c>
       <c r="D4" t="n">
-        <v>7821</v>
+        <v>9548</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1653</v>
+        <v>1755</v>
       </c>
       <c r="C5" t="n">
-        <v>5055</v>
+        <v>4538</v>
       </c>
       <c r="D5" t="n">
-        <v>3190</v>
+        <v>3294</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>887</v>
+        <v>1019</v>
       </c>
       <c r="C6" t="n">
-        <v>3478</v>
+        <v>2513</v>
       </c>
       <c r="D6" t="n">
-        <v>1301</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>417</v>
+        <v>491</v>
       </c>
       <c r="C7" t="n">
-        <v>2125</v>
+        <v>1425</v>
       </c>
       <c r="D7" t="n">
-        <v>674</v>
+        <v>654</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>152</v>
+        <v>185</v>
       </c>
       <c r="C8" t="n">
-        <v>1024</v>
+        <v>655</v>
       </c>
       <c r="D8" t="n">
-        <v>431</v>
+        <v>428</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="C9" t="n">
-        <v>435</v>
+        <v>309</v>
       </c>
       <c r="D9" t="n">
-        <v>305</v>
+        <v>309</v>
       </c>
     </row>
     <row r="10">
@@ -895,10 +895,10 @@
         <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>221</v>
+        <v>206</v>
       </c>
       <c r="D10" t="n">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="11">
@@ -909,10 +909,10 @@
         <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="D11" t="n">
-        <v>201</v>
+        <v>204</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="D12" t="n">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13">
@@ -940,7 +940,7 @@
         <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14">
@@ -951,10 +951,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -982,7 +982,7 @@
         <v>46</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -996,7 +996,7 @@
         <v>38</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1007,10 +1007,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1049,10 +1049,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6353</v>
+        <v>5819</v>
       </c>
       <c r="C2" t="n">
-        <v>9716</v>
+        <v>9997</v>
       </c>
       <c r="D2" t="n">
-        <v>33501</v>
+        <v>44892</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3688</v>
+        <v>3831</v>
       </c>
       <c r="C3" t="n">
-        <v>8948</v>
+        <v>5957</v>
       </c>
       <c r="D3" t="n">
-        <v>15905</v>
+        <v>22376</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2722</v>
+        <v>2860</v>
       </c>
       <c r="C4" t="n">
-        <v>7098</v>
+        <v>5473</v>
       </c>
       <c r="D4" t="n">
-        <v>8426</v>
+        <v>11153</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1861</v>
+        <v>1973</v>
       </c>
       <c r="C5" t="n">
-        <v>5843</v>
+        <v>5047</v>
       </c>
       <c r="D5" t="n">
-        <v>3804</v>
+        <v>4122</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1089</v>
+        <v>1209</v>
       </c>
       <c r="C6" t="n">
-        <v>4126</v>
+        <v>3358</v>
       </c>
       <c r="D6" t="n">
-        <v>1543</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>545</v>
+        <v>638</v>
       </c>
       <c r="C7" t="n">
-        <v>2673</v>
+        <v>1904</v>
       </c>
       <c r="D7" t="n">
-        <v>759</v>
+        <v>720</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>228</v>
+        <v>274</v>
       </c>
       <c r="C8" t="n">
-        <v>1476</v>
+        <v>972</v>
       </c>
       <c r="D8" t="n">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="9">
@@ -1189,10 +1189,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="C9" t="n">
-        <v>661</v>
+        <v>451</v>
       </c>
       <c r="D9" t="n">
         <v>319</v>
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C10" t="n">
-        <v>300</v>
+        <v>244</v>
       </c>
       <c r="D10" t="n">
-        <v>246</v>
+        <v>252</v>
       </c>
     </row>
     <row r="11">
@@ -1220,10 +1220,10 @@
         <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="D11" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="D12" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D13" t="n">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14">
@@ -1262,10 +1262,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -1307,7 +1307,7 @@
         <v>39</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1318,10 +1318,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1360,10 +1360,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7858</v>
+        <v>7134</v>
       </c>
       <c r="C2" t="n">
-        <v>11974</v>
+        <v>8848</v>
       </c>
       <c r="D2" t="n">
-        <v>31840</v>
+        <v>44580</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3840</v>
+        <v>3778</v>
       </c>
       <c r="C3" t="n">
-        <v>8238</v>
+        <v>6744</v>
       </c>
       <c r="D3" t="n">
-        <v>16998</v>
+        <v>23645</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2638</v>
+        <v>2767</v>
       </c>
       <c r="C4" t="n">
-        <v>7645</v>
+        <v>5568</v>
       </c>
       <c r="D4" t="n">
-        <v>9246</v>
+        <v>12322</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1946</v>
+        <v>2062</v>
       </c>
       <c r="C5" t="n">
-        <v>6227</v>
+        <v>5069</v>
       </c>
       <c r="D5" t="n">
-        <v>4273</v>
+        <v>5009</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1268</v>
+        <v>1375</v>
       </c>
       <c r="C6" t="n">
-        <v>4710</v>
+        <v>3976</v>
       </c>
       <c r="D6" t="n">
-        <v>1826</v>
+        <v>1820</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>669</v>
+        <v>774</v>
       </c>
       <c r="C7" t="n">
-        <v>3201</v>
+        <v>2487</v>
       </c>
       <c r="D7" t="n">
-        <v>843</v>
+        <v>820</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>303</v>
+        <v>369</v>
       </c>
       <c r="C8" t="n">
-        <v>1906</v>
+        <v>1318</v>
       </c>
       <c r="D8" t="n">
-        <v>489</v>
+        <v>480</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>118</v>
+        <v>145</v>
       </c>
       <c r="C9" t="n">
-        <v>956</v>
+        <v>640</v>
       </c>
       <c r="D9" t="n">
-        <v>328</v>
+        <v>333</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="C10" t="n">
-        <v>420</v>
+        <v>318</v>
       </c>
       <c r="D10" t="n">
-        <v>249</v>
+        <v>254</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="12">
@@ -1548,7 +1548,7 @@
         <v>152</v>
       </c>
       <c r="D12" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="13">
@@ -1559,10 +1559,10 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="D13" t="n">
-        <v>129</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14">
@@ -1573,10 +1573,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="15">
@@ -1590,7 +1590,7 @@
         <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -1618,7 +1618,7 @@
         <v>41</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1632,7 +1632,7 @@
         <v>35</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1671,10 +1671,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7209</v>
+        <v>6553</v>
       </c>
       <c r="C2" t="n">
-        <v>8429</v>
+        <v>6087</v>
       </c>
       <c r="D2" t="n">
-        <v>26287</v>
+        <v>36798</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4603</v>
+        <v>4739</v>
       </c>
       <c r="C3" t="n">
-        <v>12360</v>
+        <v>9763</v>
       </c>
       <c r="D3" t="n">
-        <v>18342</v>
+        <v>25349</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1798</v>
+        <v>1905</v>
       </c>
       <c r="C4" t="n">
-        <v>10014</v>
+        <v>7913</v>
       </c>
       <c r="D4" t="n">
-        <v>9030</v>
+        <v>11506</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1171</v>
+        <v>1270</v>
       </c>
       <c r="C5" t="n">
-        <v>4615</v>
+        <v>3896</v>
       </c>
       <c r="D5" t="n">
-        <v>2897</v>
+        <v>3130</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>618</v>
+        <v>715</v>
       </c>
       <c r="C6" t="n">
-        <v>3136</v>
+        <v>2437</v>
       </c>
       <c r="D6" t="n">
-        <v>826</v>
+        <v>803</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>279</v>
+        <v>340</v>
       </c>
       <c r="C7" t="n">
-        <v>1867</v>
+        <v>1291</v>
       </c>
       <c r="D7" t="n">
-        <v>479</v>
+        <v>470</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>109</v>
+        <v>133</v>
       </c>
       <c r="C8" t="n">
-        <v>936</v>
+        <v>627</v>
       </c>
       <c r="D8" t="n">
-        <v>321</v>
+        <v>326</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="C9" t="n">
-        <v>411</v>
+        <v>311</v>
       </c>
       <c r="D9" t="n">
-        <v>244</v>
+        <v>248</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C10" t="n">
-        <v>215</v>
+        <v>196</v>
       </c>
       <c r="D10" t="n">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="11">
@@ -1845,7 +1845,7 @@
         <v>148</v>
       </c>
       <c r="D11" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="12">
@@ -1856,10 +1856,10 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="D12" t="n">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="13">
@@ -1870,10 +1870,10 @@
         <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D13" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14">
@@ -1887,7 +1887,7 @@
         <v>66</v>
       </c>
       <c r="D14" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D15" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="16">
@@ -1915,7 +1915,7 @@
         <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17">
@@ -1929,7 +1929,7 @@
         <v>34</v>
       </c>
       <c r="D17" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18">
@@ -1968,10 +1968,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4356</v>
+        <v>4001</v>
       </c>
       <c r="C2" t="n">
-        <v>4450</v>
+        <v>2617</v>
       </c>
       <c r="D2" t="n">
-        <v>19474</v>
+        <v>25092</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4876</v>
+        <v>4761</v>
       </c>
       <c r="C3" t="n">
-        <v>9711</v>
+        <v>7357</v>
       </c>
       <c r="D3" t="n">
-        <v>18331</v>
+        <v>25689</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2473</v>
+        <v>2606</v>
       </c>
       <c r="C4" t="n">
-        <v>11130</v>
+        <v>8904</v>
       </c>
       <c r="D4" t="n">
-        <v>10269</v>
+        <v>13260</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1304</v>
+        <v>1410</v>
       </c>
       <c r="C5" t="n">
-        <v>6865</v>
+        <v>5621</v>
       </c>
       <c r="D5" t="n">
-        <v>3571</v>
+        <v>4140</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>734</v>
+        <v>850</v>
       </c>
       <c r="C6" t="n">
-        <v>3780</v>
+        <v>3052</v>
       </c>
       <c r="D6" t="n">
-        <v>1019</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>259</v>
+        <v>318</v>
       </c>
       <c r="C7" t="n">
-        <v>2354</v>
+        <v>1707</v>
       </c>
       <c r="D7" t="n">
-        <v>522</v>
+        <v>520</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>92</v>
+        <v>111</v>
       </c>
       <c r="C8" t="n">
-        <v>1209</v>
+        <v>822</v>
       </c>
       <c r="D8" t="n">
-        <v>330</v>
+        <v>335</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="C9" t="n">
-        <v>448</v>
+        <v>354</v>
       </c>
       <c r="D9" t="n">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>228</v>
+        <v>217</v>
       </c>
       <c r="D10" t="n">
-        <v>208</v>
+        <v>211</v>
       </c>
     </row>
     <row r="11">
@@ -2153,10 +2153,10 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="D11" t="n">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="12">
@@ -2167,10 +2167,10 @@
         <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D12" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="13">
@@ -2184,7 +2184,7 @@
         <v>64</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="14">
@@ -2198,7 +2198,7 @@
         <v>49</v>
       </c>
       <c r="D14" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15">
@@ -2212,7 +2212,7 @@
         <v>39</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -2226,7 +2226,7 @@
         <v>33</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
@@ -2265,10 +2265,10 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4173</v>
+        <v>4119</v>
       </c>
       <c r="C2" t="n">
-        <v>12725</v>
+        <v>2717</v>
       </c>
       <c r="D2" t="n">
-        <v>21679</v>
+        <v>26151</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3921</v>
+        <v>3737</v>
       </c>
       <c r="C3" t="n">
-        <v>6534</v>
+        <v>4599</v>
       </c>
       <c r="D3" t="n">
-        <v>17430</v>
+        <v>23881</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2989</v>
+        <v>3039</v>
       </c>
       <c r="C4" t="n">
-        <v>10230</v>
+        <v>7976</v>
       </c>
       <c r="D4" t="n">
-        <v>11096</v>
+        <v>14885</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1574</v>
+        <v>1690</v>
       </c>
       <c r="C5" t="n">
-        <v>8712</v>
+        <v>7016</v>
       </c>
       <c r="D5" t="n">
-        <v>4491</v>
+        <v>5414</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>877</v>
+        <v>990</v>
       </c>
       <c r="C6" t="n">
-        <v>5048</v>
+        <v>4187</v>
       </c>
       <c r="D6" t="n">
-        <v>1373</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>384</v>
+        <v>462</v>
       </c>
       <c r="C7" t="n">
-        <v>2963</v>
+        <v>2273</v>
       </c>
       <c r="D7" t="n">
-        <v>584</v>
+        <v>586</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>130</v>
+        <v>160</v>
       </c>
       <c r="C8" t="n">
-        <v>1657</v>
+        <v>1185</v>
       </c>
       <c r="D8" t="n">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="C9" t="n">
-        <v>720</v>
+        <v>535</v>
       </c>
       <c r="D9" t="n">
-        <v>260</v>
+        <v>266</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C10" t="n">
-        <v>303</v>
+        <v>264</v>
       </c>
       <c r="D10" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="11">
@@ -2464,10 +2464,10 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D11" t="n">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="12">
@@ -2478,10 +2478,10 @@
         <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D12" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13">
@@ -2492,7 +2492,7 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D13" t="n">
         <v>100</v>
@@ -2509,7 +2509,7 @@
         <v>53</v>
       </c>
       <c r="D14" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15">
@@ -2523,7 +2523,7 @@
         <v>44</v>
       </c>
       <c r="D15" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -2537,7 +2537,7 @@
         <v>35</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2517</v>
+        <v>2482</v>
       </c>
       <c r="C2" t="n">
-        <v>6265</v>
+        <v>1301</v>
       </c>
       <c r="D2" t="n">
-        <v>15122</v>
+        <v>18231</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3874</v>
+        <v>3692</v>
       </c>
       <c r="C3" t="n">
-        <v>8235</v>
+        <v>3849</v>
       </c>
       <c r="D3" t="n">
-        <v>17648</v>
+        <v>23582</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3234</v>
+        <v>3331</v>
       </c>
       <c r="C4" t="n">
-        <v>9962</v>
+        <v>7505</v>
       </c>
       <c r="D4" t="n">
-        <v>11863</v>
+        <v>15976</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1604</v>
+        <v>1755</v>
       </c>
       <c r="C5" t="n">
-        <v>10374</v>
+        <v>8252</v>
       </c>
       <c r="D5" t="n">
-        <v>4599</v>
+        <v>5732</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>695</v>
+        <v>820</v>
       </c>
       <c r="C6" t="n">
-        <v>5818</v>
+        <v>4928</v>
       </c>
       <c r="D6" t="n">
-        <v>1327</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>120</v>
+        <v>147</v>
       </c>
       <c r="C7" t="n">
-        <v>3040</v>
+        <v>2293</v>
       </c>
       <c r="D7" t="n">
-        <v>581</v>
+        <v>583</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="C8" t="n">
-        <v>1176</v>
+        <v>884</v>
       </c>
       <c r="D8" t="n">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>296</v>
+        <v>258</v>
       </c>
       <c r="D9" t="n">
-        <v>281</v>
+        <v>286</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2761,10 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D10" t="n">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="11">
@@ -2775,10 +2775,10 @@
         <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D11" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="12">
@@ -2789,7 +2789,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D12" t="n">
         <v>98</v>
@@ -2806,7 +2806,7 @@
         <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -2820,7 +2820,7 @@
         <v>43</v>
       </c>
       <c r="D14" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15">
@@ -2834,7 +2834,7 @@
         <v>34</v>
       </c>
       <c r="D15" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2609</v>
+        <v>2674</v>
       </c>
       <c r="C2" t="n">
-        <v>6980</v>
+        <v>1866</v>
       </c>
       <c r="D2" t="n">
-        <v>18649</v>
+        <v>17939</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2864</v>
+        <v>2744</v>
       </c>
       <c r="C3" t="n">
-        <v>6595</v>
+        <v>2431</v>
       </c>
       <c r="D3" t="n">
-        <v>16166</v>
+        <v>21495</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3039</v>
+        <v>3040</v>
       </c>
       <c r="C4" t="n">
-        <v>9071</v>
+        <v>5664</v>
       </c>
       <c r="D4" t="n">
-        <v>12390</v>
+        <v>16658</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1974</v>
+        <v>2112</v>
       </c>
       <c r="C5" t="n">
-        <v>10083</v>
+        <v>7829</v>
       </c>
       <c r="D5" t="n">
-        <v>5549</v>
+        <v>7032</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>926</v>
+        <v>1063</v>
       </c>
       <c r="C6" t="n">
-        <v>7618</v>
+        <v>6304</v>
       </c>
       <c r="D6" t="n">
-        <v>1718</v>
+        <v>1987</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>250</v>
+        <v>304</v>
       </c>
       <c r="C7" t="n">
-        <v>4103</v>
+        <v>3369</v>
       </c>
       <c r="D7" t="n">
-        <v>668</v>
+        <v>690</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="C8" t="n">
-        <v>1849</v>
+        <v>1398</v>
       </c>
       <c r="D8" t="n">
-        <v>391</v>
+        <v>399</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>560</v>
+        <v>461</v>
       </c>
       <c r="D9" t="n">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="10">
@@ -3072,10 +3072,10 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="D10" t="n">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="11">
@@ -3086,7 +3086,7 @@
         <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D11" t="n">
         <v>134</v>
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D13" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -3131,7 +3131,7 @@
         <v>45</v>
       </c>
       <c r="D14" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15">
@@ -3145,7 +3145,7 @@
         <v>37</v>
       </c>
       <c r="D15" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="16">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1778</v>
+        <v>1893</v>
       </c>
       <c r="C2" t="n">
-        <v>4150</v>
+        <v>1833</v>
       </c>
       <c r="D2" t="n">
-        <v>13198</v>
+        <v>13794</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2445</v>
+        <v>2387</v>
       </c>
       <c r="C3" t="n">
-        <v>6207</v>
+        <v>2033</v>
       </c>
       <c r="D3" t="n">
-        <v>15590</v>
+        <v>20105</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2754</v>
+        <v>2698</v>
       </c>
       <c r="C4" t="n">
-        <v>8129</v>
+        <v>4382</v>
       </c>
       <c r="D4" t="n">
-        <v>12603</v>
+        <v>16915</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2159</v>
+        <v>2287</v>
       </c>
       <c r="C5" t="n">
-        <v>9920</v>
+        <v>7197</v>
       </c>
       <c r="D5" t="n">
-        <v>6209</v>
+        <v>7902</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1061</v>
+        <v>1241</v>
       </c>
       <c r="C6" t="n">
-        <v>8630</v>
+        <v>7025</v>
       </c>
       <c r="D6" t="n">
-        <v>2025</v>
+        <v>2457</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>223</v>
+        <v>272</v>
       </c>
       <c r="C7" t="n">
-        <v>5140</v>
+        <v>4289</v>
       </c>
       <c r="D7" t="n">
-        <v>754</v>
+        <v>778</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="C8" t="n">
-        <v>2336</v>
+        <v>1833</v>
       </c>
       <c r="D8" t="n">
-        <v>396</v>
+        <v>414</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>597</v>
+        <v>531</v>
       </c>
       <c r="D9" t="n">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="D10" t="n">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="11">
@@ -3397,7 +3397,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D11" t="n">
         <v>135</v>
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D12" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13">
@@ -3428,7 +3428,7 @@
         <v>44</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14">
@@ -3442,7 +3442,7 @@
         <v>36</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3656</v>
+        <v>3018</v>
       </c>
       <c r="C2" t="n">
-        <v>14956</v>
+        <v>10583</v>
       </c>
       <c r="D2" t="n">
-        <v>16106</v>
+        <v>21021</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1879</v>
+        <v>1867</v>
       </c>
       <c r="C3" t="n">
-        <v>4876</v>
+        <v>1757</v>
       </c>
       <c r="D3" t="n">
-        <v>14349</v>
+        <v>18060</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2306</v>
+        <v>2251</v>
       </c>
       <c r="C4" t="n">
-        <v>7203</v>
+        <v>3279</v>
       </c>
       <c r="D4" t="n">
-        <v>12621</v>
+        <v>16860</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2143</v>
+        <v>2216</v>
       </c>
       <c r="C5" t="n">
-        <v>9043</v>
+        <v>5912</v>
       </c>
       <c r="D5" t="n">
-        <v>6818</v>
+        <v>8873</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1303</v>
+        <v>1480</v>
       </c>
       <c r="C6" t="n">
-        <v>9020</v>
+        <v>7100</v>
       </c>
       <c r="D6" t="n">
-        <v>2461</v>
+        <v>3105</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>413</v>
+        <v>509</v>
       </c>
       <c r="C7" t="n">
-        <v>6335</v>
+        <v>5279</v>
       </c>
       <c r="D7" t="n">
-        <v>895</v>
+        <v>967</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="C8" t="n">
-        <v>3264</v>
+        <v>2674</v>
       </c>
       <c r="D8" t="n">
-        <v>430</v>
+        <v>449</v>
       </c>
     </row>
     <row r="9">
@@ -3677,10 +3677,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C9" t="n">
-        <v>1108</v>
+        <v>957</v>
       </c>
       <c r="D9" t="n">
         <v>298</v>
@@ -3694,10 +3694,10 @@
         <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>324</v>
+        <v>309</v>
       </c>
       <c r="D10" t="n">
-        <v>182</v>
+        <v>185</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D11" t="n">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="D12" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14">
@@ -3764,7 +3764,7 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
         <v>18</v>
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4355</v>
+        <v>6197</v>
       </c>
       <c r="C2" t="n">
-        <v>10823</v>
+        <v>4078</v>
       </c>
       <c r="D2" t="n">
-        <v>14437</v>
+        <v>9160</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2698</v>
+        <v>2183</v>
       </c>
       <c r="C2" t="n">
-        <v>8973</v>
+        <v>6095</v>
       </c>
       <c r="D2" t="n">
-        <v>12112</v>
+        <v>15640</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2620</v>
+        <v>2560</v>
       </c>
       <c r="C3" t="n">
-        <v>7482</v>
+        <v>3888</v>
       </c>
       <c r="D3" t="n">
-        <v>15517</v>
+        <v>19647</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3158</v>
+        <v>3195</v>
       </c>
       <c r="C4" t="n">
-        <v>10229</v>
+        <v>5189</v>
       </c>
       <c r="D4" t="n">
-        <v>12848</v>
+        <v>17182</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1203</v>
+        <v>1408</v>
       </c>
       <c r="C5" t="n">
-        <v>12892</v>
+        <v>9438</v>
       </c>
       <c r="D5" t="n">
-        <v>6073</v>
+        <v>7910</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>381</v>
+        <v>470</v>
       </c>
       <c r="C6" t="n">
-        <v>7711</v>
+        <v>6495</v>
       </c>
       <c r="D6" t="n">
-        <v>1953</v>
+        <v>2345</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>74</v>
+        <v>95</v>
       </c>
       <c r="C7" t="n">
-        <v>3198</v>
+        <v>2620</v>
       </c>
       <c r="D7" t="n">
-        <v>526</v>
+        <v>563</v>
       </c>
     </row>
     <row r="8">
@@ -4285,10 +4285,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C8" t="n">
-        <v>1085</v>
+        <v>937</v>
       </c>
       <c r="D8" t="n">
         <v>292</v>
@@ -4302,10 +4302,10 @@
         <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>317</v>
+        <v>302</v>
       </c>
       <c r="D9" t="n">
-        <v>178</v>
+        <v>181</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D10" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="D11" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="12">
@@ -4347,7 +4347,7 @@
         <v>49</v>
       </c>
       <c r="D12" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13">
@@ -4372,7 +4372,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D14" t="n">
         <v>17</v>
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6545</v>
+        <v>6748</v>
       </c>
       <c r="C2" t="n">
-        <v>5922</v>
+        <v>5667</v>
       </c>
       <c r="D2" t="n">
-        <v>23283</v>
+        <v>11190</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1852</v>
+        <v>2633</v>
       </c>
       <c r="C3" t="n">
-        <v>5454</v>
+        <v>2055</v>
       </c>
       <c r="D3" t="n">
-        <v>3064</v>
+        <v>2178</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>79</v>
       </c>
       <c r="C4" t="n">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D4" t="n">
         <v>1538</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C5" t="n">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C6" t="n">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="D6" t="n">
-        <v>816</v>
+        <v>808</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>350</v>
       </c>
       <c r="D7" t="n">
-        <v>538</v>
+        <v>546</v>
       </c>
     </row>
     <row r="8">
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4672</v>
+        <v>4609</v>
       </c>
       <c r="C2" t="n">
-        <v>5671</v>
+        <v>5494</v>
       </c>
       <c r="D2" t="n">
-        <v>31084</v>
+        <v>27662</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3443</v>
+        <v>3852</v>
       </c>
       <c r="C3" t="n">
-        <v>4931</v>
+        <v>3560</v>
       </c>
       <c r="D3" t="n">
-        <v>6235</v>
+        <v>3531</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>839</v>
+        <v>1177</v>
       </c>
       <c r="C4" t="n">
-        <v>3239</v>
+        <v>1266</v>
       </c>
       <c r="D4" t="n">
-        <v>1798</v>
+        <v>1620</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="D5" t="n">
-        <v>1198</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C6" t="n">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="D6" t="n">
-        <v>859</v>
+        <v>864</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C7" t="n">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>584</v>
+        <v>589</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C8" t="n">
         <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="9">
@@ -4921,10 +4921,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C9" t="n">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D9" t="n">
         <v>363</v>
@@ -4935,7 +4935,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C10" t="n">
         <v>192</v>
@@ -4949,7 +4949,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C11" t="n">
         <v>166</v>
@@ -4966,7 +4966,7 @@
         <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D12" t="n">
         <v>206</v>
@@ -4983,7 +4983,7 @@
         <v>103</v>
       </c>
       <c r="D13" t="n">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="14">
@@ -4997,7 +4997,7 @@
         <v>83</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C15" t="n">
         <v>74</v>
@@ -5025,7 +5025,7 @@
         <v>71</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="17">
@@ -5039,7 +5039,7 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5050,7 +5050,7 @@
         <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
         <v>59</v>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4759</v>
+        <v>4642</v>
       </c>
       <c r="C2" t="n">
-        <v>10051</v>
+        <v>5351</v>
       </c>
       <c r="D2" t="n">
-        <v>23682</v>
+        <v>41917</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3356</v>
+        <v>3480</v>
       </c>
       <c r="C3" t="n">
-        <v>4619</v>
+        <v>3994</v>
       </c>
       <c r="D3" t="n">
-        <v>9761</v>
+        <v>7137</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1786</v>
+        <v>2129</v>
       </c>
       <c r="C4" t="n">
-        <v>4113</v>
+        <v>2538</v>
       </c>
       <c r="D4" t="n">
-        <v>2595</v>
+        <v>1937</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>399</v>
+        <v>543</v>
       </c>
       <c r="C5" t="n">
-        <v>1838</v>
+        <v>785</v>
       </c>
       <c r="D5" t="n">
-        <v>1259</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C6" t="n">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="D6" t="n">
-        <v>908</v>
+        <v>910</v>
       </c>
     </row>
     <row r="7">
@@ -5207,10 +5207,10 @@
         <v>160</v>
       </c>
       <c r="C7" t="n">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C8" t="n">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="D8" t="n">
-        <v>454</v>
+        <v>462</v>
       </c>
     </row>
     <row r="9">
@@ -5235,10 +5235,10 @@
         <v>91</v>
       </c>
       <c r="C9" t="n">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="D9" t="n">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="10">
@@ -5246,7 +5246,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C10" t="n">
         <v>210</v>
@@ -5260,7 +5260,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C11" t="n">
         <v>177</v>
@@ -5277,10 +5277,10 @@
         <v>31</v>
       </c>
       <c r="C12" t="n">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D12" t="n">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="13">
@@ -5291,7 +5291,7 @@
         <v>21</v>
       </c>
       <c r="C13" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D13" t="n">
         <v>173</v>
@@ -5305,10 +5305,10 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
         <v>77</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="16">
@@ -5333,7 +5333,7 @@
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
         <v>99</v>
@@ -5350,7 +5350,7 @@
         <v>69</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18">
@@ -5375,7 +5375,7 @@
         <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D19" t="n">
         <v>41</v>
@@ -5406,7 +5406,7 @@
         <v>122</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4513</v>
+        <v>6068</v>
       </c>
       <c r="C2" t="n">
-        <v>6892</v>
+        <v>6694</v>
       </c>
       <c r="D2" t="n">
-        <v>26447</v>
+        <v>43816</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3295</v>
+        <v>3316</v>
       </c>
       <c r="C3" t="n">
-        <v>6417</v>
+        <v>4084</v>
       </c>
       <c r="D3" t="n">
-        <v>11189</v>
+        <v>11921</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2152</v>
+        <v>2391</v>
       </c>
       <c r="C4" t="n">
-        <v>4255</v>
+        <v>3267</v>
       </c>
       <c r="D4" t="n">
-        <v>3823</v>
+        <v>2826</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>894</v>
+        <v>1097</v>
       </c>
       <c r="C5" t="n">
-        <v>2979</v>
+        <v>1669</v>
       </c>
       <c r="D5" t="n">
-        <v>1439</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>237</v>
+        <v>299</v>
       </c>
       <c r="C6" t="n">
-        <v>1066</v>
+        <v>544</v>
       </c>
       <c r="D6" t="n">
-        <v>956</v>
+        <v>950</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C7" t="n">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="D7" t="n">
-        <v>666</v>
+        <v>659</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C8" t="n">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D8" t="n">
-        <v>471</v>
+        <v>484</v>
       </c>
     </row>
     <row r="9">
@@ -5546,10 +5546,10 @@
         <v>97</v>
       </c>
       <c r="C9" t="n">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D9" t="n">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="10">
@@ -5560,10 +5560,10 @@
         <v>70</v>
       </c>
       <c r="C10" t="n">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D10" t="n">
-        <v>342</v>
+        <v>346</v>
       </c>
     </row>
     <row r="11">
@@ -5574,7 +5574,7 @@
         <v>50</v>
       </c>
       <c r="C11" t="n">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D11" t="n">
         <v>286</v>
@@ -5588,10 +5588,10 @@
         <v>33</v>
       </c>
       <c r="C12" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D12" t="n">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="13">
@@ -5602,7 +5602,7 @@
         <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="D13" t="n">
         <v>176</v>
@@ -5616,7 +5616,7 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D14" t="n">
         <v>149</v>
@@ -5630,10 +5630,10 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="16">
@@ -5644,7 +5644,7 @@
         <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D16" t="n">
         <v>100</v>
@@ -5661,7 +5661,7 @@
         <v>69</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18">
@@ -5686,10 +5686,10 @@
         <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D19" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20">
@@ -5717,7 +5717,7 @@
         <v>137</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6969</v>
+        <v>5727</v>
       </c>
       <c r="C2" t="n">
-        <v>10996</v>
+        <v>12752</v>
       </c>
       <c r="D2" t="n">
-        <v>22548</v>
+        <v>35502</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2817</v>
+        <v>3374</v>
       </c>
       <c r="C3" t="n">
-        <v>5456</v>
+        <v>4438</v>
       </c>
       <c r="D3" t="n">
-        <v>11968</v>
+        <v>14985</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1668</v>
+        <v>1760</v>
       </c>
       <c r="C4" t="n">
-        <v>4439</v>
+        <v>3045</v>
       </c>
       <c r="D4" t="n">
-        <v>4406</v>
+        <v>3843</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>783</v>
+        <v>916</v>
       </c>
       <c r="C5" t="n">
-        <v>2623</v>
+        <v>1814</v>
       </c>
       <c r="D5" t="n">
-        <v>1452</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>266</v>
+        <v>327</v>
       </c>
       <c r="C6" t="n">
-        <v>1354</v>
+        <v>748</v>
       </c>
       <c r="D6" t="n">
-        <v>790</v>
+        <v>767</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="C7" t="n">
-        <v>440</v>
+        <v>284</v>
       </c>
       <c r="D7" t="n">
-        <v>523</v>
+        <v>513</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="D8" t="n">
-        <v>352</v>
+        <v>364</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D9" t="n">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C10" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D10" t="n">
-        <v>233</v>
+        <v>237</v>
       </c>
     </row>
     <row r="11">
@@ -5885,10 +5885,10 @@
         <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D11" t="n">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C12" t="n">
         <v>92</v>
       </c>
       <c r="D12" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D13" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="14">
@@ -5927,10 +5927,10 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D14" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15">
@@ -5944,7 +5944,7 @@
         <v>45</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -5958,7 +5958,7 @@
         <v>38</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -5980,7 +5980,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
         <v>33</v>
@@ -6028,7 +6028,7 @@
         <v>75</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5996</v>
+        <v>6334</v>
       </c>
       <c r="C2" t="n">
-        <v>11750</v>
+        <v>5724</v>
       </c>
       <c r="D2" t="n">
-        <v>24101</v>
+        <v>36074</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4051</v>
+        <v>3779</v>
       </c>
       <c r="C3" t="n">
-        <v>7444</v>
+        <v>8003</v>
       </c>
       <c r="D3" t="n">
-        <v>12864</v>
+        <v>17328</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1958</v>
+        <v>2258</v>
       </c>
       <c r="C4" t="n">
-        <v>4951</v>
+        <v>3824</v>
       </c>
       <c r="D4" t="n">
-        <v>5796</v>
+        <v>5935</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1079</v>
+        <v>1196</v>
       </c>
       <c r="C5" t="n">
-        <v>3589</v>
+        <v>2479</v>
       </c>
       <c r="D5" t="n">
-        <v>1961</v>
+        <v>1710</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>484</v>
+        <v>571</v>
       </c>
       <c r="C6" t="n">
-        <v>2056</v>
+        <v>1352</v>
       </c>
       <c r="D6" t="n">
-        <v>905</v>
+        <v>842</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>192</v>
       </c>
       <c r="C7" t="n">
-        <v>950</v>
+        <v>547</v>
       </c>
       <c r="D7" t="n">
-        <v>562</v>
+        <v>550</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="C8" t="n">
-        <v>339</v>
+        <v>256</v>
       </c>
       <c r="D8" t="n">
-        <v>380</v>
+        <v>388</v>
       </c>
     </row>
     <row r="9">
@@ -6168,10 +6168,10 @@
         <v>47</v>
       </c>
       <c r="C9" t="n">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="D9" t="n">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C10" t="n">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D10" t="n">
-        <v>234</v>
+        <v>240</v>
       </c>
     </row>
     <row r="11">
@@ -6196,7 +6196,7 @@
         <v>23</v>
       </c>
       <c r="C11" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D11" t="n">
         <v>199</v>
@@ -6210,10 +6210,10 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D12" t="n">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="13">
@@ -6221,10 +6221,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D13" t="n">
         <v>119</v>
@@ -6252,7 +6252,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D15" t="n">
         <v>80</v>
@@ -6269,7 +6269,7 @@
         <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -6297,7 +6297,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C19" t="n">
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -6339,7 +6339,7 @@
         <v>83</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4912</v>
+        <v>5828</v>
       </c>
       <c r="C2" t="n">
-        <v>8291</v>
+        <v>6587</v>
       </c>
       <c r="D2" t="n">
-        <v>21114</v>
+        <v>42694</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4097</v>
+        <v>4124</v>
       </c>
       <c r="C3" t="n">
-        <v>8430</v>
+        <v>5851</v>
       </c>
       <c r="D3" t="n">
-        <v>13666</v>
+        <v>19079</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2557</v>
+        <v>2597</v>
       </c>
       <c r="C4" t="n">
-        <v>6164</v>
+        <v>6111</v>
       </c>
       <c r="D4" t="n">
-        <v>6853</v>
+        <v>7942</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1315</v>
+        <v>1500</v>
       </c>
       <c r="C5" t="n">
-        <v>4246</v>
+        <v>3163</v>
       </c>
       <c r="D5" t="n">
-        <v>2600</v>
+        <v>2412</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>703</v>
+        <v>803</v>
       </c>
       <c r="C6" t="n">
-        <v>2827</v>
+        <v>1931</v>
       </c>
       <c r="D6" t="n">
-        <v>1066</v>
+        <v>988</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>276</v>
+        <v>333</v>
       </c>
       <c r="C7" t="n">
-        <v>1503</v>
+        <v>959</v>
       </c>
       <c r="D7" t="n">
-        <v>616</v>
+        <v>595</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>96</v>
+        <v>114</v>
       </c>
       <c r="C8" t="n">
-        <v>644</v>
+        <v>404</v>
       </c>
       <c r="D8" t="n">
-        <v>402</v>
+        <v>407</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>271</v>
+        <v>232</v>
       </c>
       <c r="D9" t="n">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="10">
@@ -6493,10 +6493,10 @@
         <v>36</v>
       </c>
       <c r="C10" t="n">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="D10" t="n">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>200</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D12" t="n">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13">
@@ -6535,7 +6535,7 @@
         <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D13" t="n">
         <v>121</v>
@@ -6546,10 +6546,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
         <v>99</v>
@@ -6566,7 +6566,7 @@
         <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -6580,7 +6580,7 @@
         <v>43</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -6594,7 +6594,7 @@
         <v>37</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -6608,7 +6608,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -6630,7 +6630,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C20" t="n">
         <v>29</v>
@@ -6647,10 +6647,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_population_iteration_52_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_52_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5505</v>
+        <v>6042</v>
       </c>
       <c r="C2" t="n">
-        <v>8416</v>
+        <v>15102</v>
       </c>
       <c r="D2" t="n">
-        <v>40522</v>
+        <v>28063</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4030</v>
+        <v>3395</v>
       </c>
       <c r="C3" t="n">
-        <v>5429</v>
+        <v>5080</v>
       </c>
       <c r="D3" t="n">
-        <v>21166</v>
+        <v>12690</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2842</v>
+        <v>2662</v>
       </c>
       <c r="C4" t="n">
-        <v>5849</v>
+        <v>4761</v>
       </c>
       <c r="D4" t="n">
-        <v>9548</v>
+        <v>6520</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1755</v>
+        <v>1773</v>
       </c>
       <c r="C5" t="n">
-        <v>4538</v>
+        <v>3607</v>
       </c>
       <c r="D5" t="n">
-        <v>3294</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1019</v>
+        <v>1030</v>
       </c>
       <c r="C6" t="n">
-        <v>2513</v>
+        <v>2653</v>
       </c>
       <c r="D6" t="n">
-        <v>1197</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>491</v>
+        <v>508</v>
       </c>
       <c r="C7" t="n">
-        <v>1425</v>
+        <v>1847</v>
       </c>
       <c r="D7" t="n">
-        <v>654</v>
+        <v>663</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="C8" t="n">
-        <v>655</v>
+        <v>956</v>
       </c>
       <c r="D8" t="n">
-        <v>428</v>
+        <v>433</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C9" t="n">
-        <v>309</v>
+        <v>399</v>
       </c>
       <c r="D9" t="n">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="10">
@@ -895,10 +895,10 @@
         <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="D10" t="n">
-        <v>246</v>
+        <v>243</v>
       </c>
     </row>
     <row r="11">
@@ -909,10 +909,10 @@
         <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D11" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="12">
@@ -926,7 +926,7 @@
         <v>128</v>
       </c>
       <c r="D12" t="n">
-        <v>161</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13">
@@ -940,7 +940,7 @@
         <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14">
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -996,7 +996,7 @@
         <v>38</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1010,7 +1010,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1052,7 +1052,7 @@
         <v>98</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5819</v>
+        <v>7717</v>
       </c>
       <c r="C2" t="n">
-        <v>9997</v>
+        <v>18010</v>
       </c>
       <c r="D2" t="n">
-        <v>44892</v>
+        <v>28674</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3831</v>
+        <v>3707</v>
       </c>
       <c r="C3" t="n">
-        <v>5957</v>
+        <v>8551</v>
       </c>
       <c r="D3" t="n">
-        <v>22376</v>
+        <v>13927</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2860</v>
+        <v>2553</v>
       </c>
       <c r="C4" t="n">
-        <v>5473</v>
+        <v>4818</v>
       </c>
       <c r="D4" t="n">
-        <v>11153</v>
+        <v>7266</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1973</v>
+        <v>1912</v>
       </c>
       <c r="C5" t="n">
-        <v>5047</v>
+        <v>4040</v>
       </c>
       <c r="D5" t="n">
-        <v>4122</v>
+        <v>3160</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1209</v>
+        <v>1245</v>
       </c>
       <c r="C6" t="n">
-        <v>3358</v>
+        <v>3066</v>
       </c>
       <c r="D6" t="n">
-        <v>1503</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>638</v>
+        <v>657</v>
       </c>
       <c r="C7" t="n">
-        <v>1904</v>
+        <v>2191</v>
       </c>
       <c r="D7" t="n">
-        <v>720</v>
+        <v>737</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>274</v>
+        <v>287</v>
       </c>
       <c r="C8" t="n">
-        <v>972</v>
+        <v>1348</v>
       </c>
       <c r="D8" t="n">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="C9" t="n">
-        <v>451</v>
+        <v>629</v>
       </c>
       <c r="D9" t="n">
-        <v>319</v>
+        <v>322</v>
       </c>
     </row>
     <row r="10">
@@ -1206,10 +1206,10 @@
         <v>45</v>
       </c>
       <c r="C10" t="n">
-        <v>244</v>
+        <v>292</v>
       </c>
       <c r="D10" t="n">
-        <v>252</v>
+        <v>246</v>
       </c>
     </row>
     <row r="11">
@@ -1220,10 +1220,10 @@
         <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="D11" t="n">
-        <v>205</v>
+        <v>208</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D12" t="n">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14">
@@ -1262,7 +1262,7 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D14" t="n">
         <v>101</v>
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -1290,7 +1290,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D16" t="n">
         <v>66</v>
@@ -1304,10 +1304,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1321,7 +1321,7 @@
         <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1360,10 +1360,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7134</v>
+        <v>8821</v>
       </c>
       <c r="C2" t="n">
-        <v>8848</v>
+        <v>12192</v>
       </c>
       <c r="D2" t="n">
-        <v>44580</v>
+        <v>26341</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3778</v>
+        <v>4365</v>
       </c>
       <c r="C3" t="n">
-        <v>6744</v>
+        <v>11060</v>
       </c>
       <c r="D3" t="n">
-        <v>23645</v>
+        <v>14901</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2767</v>
+        <v>2570</v>
       </c>
       <c r="C4" t="n">
-        <v>5568</v>
+        <v>6320</v>
       </c>
       <c r="D4" t="n">
-        <v>12322</v>
+        <v>8068</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2062</v>
+        <v>1935</v>
       </c>
       <c r="C5" t="n">
-        <v>5069</v>
+        <v>4292</v>
       </c>
       <c r="D5" t="n">
-        <v>5009</v>
+        <v>3624</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1375</v>
+        <v>1383</v>
       </c>
       <c r="C6" t="n">
-        <v>3976</v>
+        <v>3410</v>
       </c>
       <c r="D6" t="n">
-        <v>1820</v>
+        <v>1611</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>774</v>
+        <v>803</v>
       </c>
       <c r="C7" t="n">
-        <v>2487</v>
+        <v>2528</v>
       </c>
       <c r="D7" t="n">
-        <v>820</v>
+        <v>809</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>369</v>
+        <v>386</v>
       </c>
       <c r="C8" t="n">
-        <v>1318</v>
+        <v>1686</v>
       </c>
       <c r="D8" t="n">
-        <v>480</v>
+        <v>491</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="C9" t="n">
-        <v>640</v>
+        <v>897</v>
       </c>
       <c r="D9" t="n">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C10" t="n">
-        <v>318</v>
+        <v>417</v>
       </c>
       <c r="D10" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="11">
@@ -1531,7 +1531,7 @@
         <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="D11" t="n">
         <v>208</v>
@@ -1545,7 +1545,7 @@
         <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="D12" t="n">
         <v>165</v>
@@ -1562,7 +1562,7 @@
         <v>118</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="14">
@@ -1573,7 +1573,7 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D14" t="n">
         <v>102</v>
@@ -1587,10 +1587,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -1615,10 +1615,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1632,7 +1632,7 @@
         <v>35</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1671,10 +1671,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6553</v>
+        <v>7995</v>
       </c>
       <c r="C2" t="n">
-        <v>6087</v>
+        <v>8290</v>
       </c>
       <c r="D2" t="n">
-        <v>36798</v>
+        <v>21644</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4739</v>
+        <v>4978</v>
       </c>
       <c r="C3" t="n">
-        <v>9763</v>
+        <v>14628</v>
       </c>
       <c r="D3" t="n">
-        <v>25349</v>
+        <v>16133</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1905</v>
+        <v>1787</v>
       </c>
       <c r="C4" t="n">
-        <v>7913</v>
+        <v>7639</v>
       </c>
       <c r="D4" t="n">
-        <v>11506</v>
+        <v>7849</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1270</v>
+        <v>1277</v>
       </c>
       <c r="C5" t="n">
-        <v>3896</v>
+        <v>3341</v>
       </c>
       <c r="D5" t="n">
-        <v>3130</v>
+        <v>2552</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>715</v>
+        <v>741</v>
       </c>
       <c r="C6" t="n">
-        <v>2437</v>
+        <v>2477</v>
       </c>
       <c r="D6" t="n">
-        <v>803</v>
+        <v>792</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>340</v>
+        <v>356</v>
       </c>
       <c r="C7" t="n">
-        <v>1291</v>
+        <v>1652</v>
       </c>
       <c r="D7" t="n">
-        <v>470</v>
+        <v>481</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="C8" t="n">
-        <v>627</v>
+        <v>879</v>
       </c>
       <c r="D8" t="n">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C9" t="n">
-        <v>311</v>
+        <v>408</v>
       </c>
       <c r="D9" t="n">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="10">
@@ -1828,7 +1828,7 @@
         <v>27</v>
       </c>
       <c r="C10" t="n">
-        <v>196</v>
+        <v>215</v>
       </c>
       <c r="D10" t="n">
         <v>203</v>
@@ -1842,7 +1842,7 @@
         <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="D11" t="n">
         <v>161</v>
@@ -1859,7 +1859,7 @@
         <v>115</v>
       </c>
       <c r="D12" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="13">
@@ -1870,7 +1870,7 @@
         <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
         <v>99</v>
@@ -1884,10 +1884,10 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D14" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="15">
@@ -1912,10 +1912,10 @@
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17">
@@ -1929,7 +1929,7 @@
         <v>34</v>
       </c>
       <c r="D17" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18">
@@ -1968,10 +1968,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4001</v>
+        <v>4816</v>
       </c>
       <c r="C2" t="n">
-        <v>2617</v>
+        <v>3842</v>
       </c>
       <c r="D2" t="n">
-        <v>25092</v>
+        <v>14696</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4761</v>
+        <v>5357</v>
       </c>
       <c r="C3" t="n">
-        <v>7357</v>
+        <v>10610</v>
       </c>
       <c r="D3" t="n">
-        <v>25689</v>
+        <v>15953</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2606</v>
+        <v>2583</v>
       </c>
       <c r="C4" t="n">
-        <v>8904</v>
+        <v>11061</v>
       </c>
       <c r="D4" t="n">
-        <v>13260</v>
+        <v>9033</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1410</v>
+        <v>1395</v>
       </c>
       <c r="C5" t="n">
-        <v>5621</v>
+        <v>5206</v>
       </c>
       <c r="D5" t="n">
-        <v>4140</v>
+        <v>3184</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>850</v>
+        <v>886</v>
       </c>
       <c r="C6" t="n">
-        <v>3052</v>
+        <v>2902</v>
       </c>
       <c r="D6" t="n">
-        <v>1040</v>
+        <v>974</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>318</v>
+        <v>335</v>
       </c>
       <c r="C7" t="n">
-        <v>1707</v>
+        <v>2023</v>
       </c>
       <c r="D7" t="n">
-        <v>520</v>
+        <v>525</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C8" t="n">
-        <v>822</v>
+        <v>1130</v>
       </c>
       <c r="D8" t="n">
-        <v>335</v>
+        <v>339</v>
       </c>
     </row>
     <row r="9">
@@ -2125,10 +2125,10 @@
         <v>43</v>
       </c>
       <c r="C9" t="n">
-        <v>354</v>
+        <v>465</v>
       </c>
       <c r="D9" t="n">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="10">
@@ -2139,7 +2139,7 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>217</v>
+        <v>233</v>
       </c>
       <c r="D10" t="n">
         <v>211</v>
@@ -2153,7 +2153,7 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="D11" t="n">
         <v>166</v>
@@ -2167,7 +2167,7 @@
         <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D12" t="n">
         <v>131</v>
@@ -2181,10 +2181,10 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D13" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14">
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16">
@@ -2226,7 +2226,7 @@
         <v>33</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17">
@@ -2265,10 +2265,10 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4119</v>
+        <v>4932</v>
       </c>
       <c r="C2" t="n">
-        <v>2717</v>
+        <v>5230</v>
       </c>
       <c r="D2" t="n">
-        <v>26151</v>
+        <v>11288</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3737</v>
+        <v>4349</v>
       </c>
       <c r="C3" t="n">
-        <v>4599</v>
+        <v>6589</v>
       </c>
       <c r="D3" t="n">
-        <v>23881</v>
+        <v>14710</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3039</v>
+        <v>3213</v>
       </c>
       <c r="C4" t="n">
-        <v>7976</v>
+        <v>10610</v>
       </c>
       <c r="D4" t="n">
-        <v>14885</v>
+        <v>9887</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1690</v>
+        <v>1683</v>
       </c>
       <c r="C5" t="n">
-        <v>7016</v>
+        <v>7851</v>
       </c>
       <c r="D5" t="n">
-        <v>5414</v>
+        <v>3985</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>990</v>
+        <v>1020</v>
       </c>
       <c r="C6" t="n">
-        <v>4187</v>
+        <v>3941</v>
       </c>
       <c r="D6" t="n">
-        <v>1472</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>462</v>
+        <v>481</v>
       </c>
       <c r="C7" t="n">
-        <v>2273</v>
+        <v>2421</v>
       </c>
       <c r="D7" t="n">
-        <v>586</v>
+        <v>581</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="C8" t="n">
-        <v>1185</v>
+        <v>1499</v>
       </c>
       <c r="D8" t="n">
-        <v>355</v>
+        <v>359</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C9" t="n">
-        <v>535</v>
+        <v>717</v>
       </c>
       <c r="D9" t="n">
-        <v>266</v>
+        <v>263</v>
       </c>
     </row>
     <row r="10">
@@ -2450,10 +2450,10 @@
         <v>19</v>
       </c>
       <c r="C10" t="n">
-        <v>264</v>
+        <v>317</v>
       </c>
       <c r="D10" t="n">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="11">
@@ -2464,7 +2464,7 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="D11" t="n">
         <v>169</v>
@@ -2478,7 +2478,7 @@
         <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="D12" t="n">
         <v>133</v>
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14">
@@ -2506,7 +2506,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
         <v>63</v>
@@ -2523,7 +2523,7 @@
         <v>44</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D16" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
@@ -2562,7 +2562,7 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D18" t="n">
         <v>13</v>
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2482</v>
+        <v>2923</v>
       </c>
       <c r="C2" t="n">
-        <v>1301</v>
+        <v>2438</v>
       </c>
       <c r="D2" t="n">
-        <v>18231</v>
+        <v>7895</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3692</v>
+        <v>4367</v>
       </c>
       <c r="C3" t="n">
-        <v>3849</v>
+        <v>5932</v>
       </c>
       <c r="D3" t="n">
-        <v>23582</v>
+        <v>14024</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3331</v>
+        <v>3530</v>
       </c>
       <c r="C4" t="n">
-        <v>7505</v>
+        <v>10095</v>
       </c>
       <c r="D4" t="n">
-        <v>15976</v>
+        <v>10515</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1755</v>
+        <v>1771</v>
       </c>
       <c r="C5" t="n">
-        <v>8252</v>
+        <v>9632</v>
       </c>
       <c r="D5" t="n">
-        <v>5732</v>
+        <v>4209</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>820</v>
+        <v>859</v>
       </c>
       <c r="C6" t="n">
-        <v>4928</v>
+        <v>4790</v>
       </c>
       <c r="D6" t="n">
-        <v>1427</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="C7" t="n">
-        <v>2293</v>
+        <v>2603</v>
       </c>
       <c r="D7" t="n">
-        <v>583</v>
+        <v>581</v>
       </c>
     </row>
     <row r="8">
@@ -2730,10 +2730,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C8" t="n">
-        <v>884</v>
+        <v>1158</v>
       </c>
       <c r="D8" t="n">
         <v>377</v>
@@ -2747,10 +2747,10 @@
         <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>258</v>
+        <v>310</v>
       </c>
       <c r="D9" t="n">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="10">
@@ -2761,7 +2761,7 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="D10" t="n">
         <v>165</v>
@@ -2775,7 +2775,7 @@
         <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="D11" t="n">
         <v>130</v>
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13">
@@ -2803,7 +2803,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D13" t="n">
         <v>61</v>
@@ -2820,7 +2820,7 @@
         <v>43</v>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16">
@@ -2859,7 +2859,7 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D17" t="n">
         <v>12</v>
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2674</v>
+        <v>3528</v>
       </c>
       <c r="C2" t="n">
-        <v>1866</v>
+        <v>9689</v>
       </c>
       <c r="D2" t="n">
-        <v>17939</v>
+        <v>10036</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2744</v>
+        <v>3228</v>
       </c>
       <c r="C3" t="n">
-        <v>2431</v>
+        <v>3879</v>
       </c>
       <c r="D3" t="n">
-        <v>21495</v>
+        <v>12382</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3040</v>
+        <v>3405</v>
       </c>
       <c r="C4" t="n">
-        <v>5664</v>
+        <v>8023</v>
       </c>
       <c r="D4" t="n">
-        <v>16658</v>
+        <v>10734</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2112</v>
+        <v>2181</v>
       </c>
       <c r="C5" t="n">
-        <v>7829</v>
+        <v>9636</v>
       </c>
       <c r="D5" t="n">
-        <v>7032</v>
+        <v>4989</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1063</v>
+        <v>1086</v>
       </c>
       <c r="C6" t="n">
-        <v>6304</v>
+        <v>6885</v>
       </c>
       <c r="D6" t="n">
-        <v>1987</v>
+        <v>1637</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>304</v>
+        <v>329</v>
       </c>
       <c r="C7" t="n">
-        <v>3369</v>
+        <v>3484</v>
       </c>
       <c r="D7" t="n">
-        <v>690</v>
+        <v>666</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C8" t="n">
-        <v>1398</v>
+        <v>1704</v>
       </c>
       <c r="D8" t="n">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="9">
@@ -3058,10 +3058,10 @@
         <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>461</v>
+        <v>593</v>
       </c>
       <c r="D9" t="n">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="10">
@@ -3072,7 +3072,7 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>209</v>
+        <v>227</v>
       </c>
       <c r="D10" t="n">
         <v>174</v>
@@ -3086,7 +3086,7 @@
         <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="D11" t="n">
         <v>134</v>
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13">
@@ -3114,7 +3114,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D13" t="n">
         <v>61</v>
@@ -3128,7 +3128,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D14" t="n">
         <v>47</v>
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D15" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1893</v>
+        <v>2443</v>
       </c>
       <c r="C2" t="n">
-        <v>1833</v>
+        <v>5046</v>
       </c>
       <c r="D2" t="n">
-        <v>13794</v>
+        <v>8398</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2387</v>
+        <v>2913</v>
       </c>
       <c r="C3" t="n">
-        <v>2033</v>
+        <v>5570</v>
       </c>
       <c r="D3" t="n">
-        <v>20105</v>
+        <v>11545</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2698</v>
+        <v>3087</v>
       </c>
       <c r="C4" t="n">
-        <v>4382</v>
+        <v>6416</v>
       </c>
       <c r="D4" t="n">
-        <v>16915</v>
+        <v>10716</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2287</v>
+        <v>2411</v>
       </c>
       <c r="C5" t="n">
-        <v>7197</v>
+        <v>9232</v>
       </c>
       <c r="D5" t="n">
-        <v>7902</v>
+        <v>5491</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1241</v>
+        <v>1269</v>
       </c>
       <c r="C6" t="n">
-        <v>7025</v>
+        <v>7995</v>
       </c>
       <c r="D6" t="n">
-        <v>2457</v>
+        <v>1955</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>272</v>
+        <v>297</v>
       </c>
       <c r="C7" t="n">
-        <v>4289</v>
+        <v>4521</v>
       </c>
       <c r="D7" t="n">
-        <v>778</v>
+        <v>738</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C8" t="n">
-        <v>1833</v>
+        <v>2144</v>
       </c>
       <c r="D8" t="n">
-        <v>414</v>
+        <v>410</v>
       </c>
     </row>
     <row r="9">
@@ -3369,10 +3369,10 @@
         <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>531</v>
+        <v>667</v>
       </c>
       <c r="D9" t="n">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="10">
@@ -3383,7 +3383,7 @@
         <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>214</v>
+        <v>233</v>
       </c>
       <c r="D10" t="n">
         <v>177</v>
@@ -3397,7 +3397,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D11" t="n">
         <v>135</v>
@@ -3411,7 +3411,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D12" t="n">
         <v>92</v>
@@ -3425,7 +3425,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D13" t="n">
         <v>63</v>
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
+        <v>37</v>
+      </c>
+      <c r="D14" t="n">
         <v>36</v>
-      </c>
-      <c r="D14" t="n">
-        <v>35</v>
       </c>
     </row>
     <row r="15">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3018</v>
+        <v>3616</v>
       </c>
       <c r="C2" t="n">
-        <v>10583</v>
+        <v>14358</v>
       </c>
       <c r="D2" t="n">
-        <v>21021</v>
+        <v>11026</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1867</v>
+        <v>2316</v>
       </c>
       <c r="C3" t="n">
-        <v>1757</v>
+        <v>4824</v>
       </c>
       <c r="D3" t="n">
-        <v>18060</v>
+        <v>10428</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2251</v>
+        <v>2630</v>
       </c>
       <c r="C4" t="n">
-        <v>3279</v>
+        <v>5871</v>
       </c>
       <c r="D4" t="n">
-        <v>16860</v>
+        <v>10509</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2216</v>
+        <v>2427</v>
       </c>
       <c r="C5" t="n">
-        <v>5912</v>
+        <v>7904</v>
       </c>
       <c r="D5" t="n">
-        <v>8873</v>
+        <v>6026</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1480</v>
+        <v>1512</v>
       </c>
       <c r="C6" t="n">
-        <v>7100</v>
+        <v>8481</v>
       </c>
       <c r="D6" t="n">
-        <v>3105</v>
+        <v>2371</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>509</v>
+        <v>534</v>
       </c>
       <c r="C7" t="n">
-        <v>5279</v>
+        <v>5778</v>
       </c>
       <c r="D7" t="n">
-        <v>967</v>
+        <v>873</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="C8" t="n">
-        <v>2674</v>
+        <v>2958</v>
       </c>
       <c r="D8" t="n">
-        <v>449</v>
+        <v>441</v>
       </c>
     </row>
     <row r="9">
@@ -3680,10 +3680,10 @@
         <v>23</v>
       </c>
       <c r="C9" t="n">
-        <v>957</v>
+        <v>1150</v>
       </c>
       <c r="D9" t="n">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="10">
@@ -3694,7 +3694,7 @@
         <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>309</v>
+        <v>362</v>
       </c>
       <c r="D10" t="n">
         <v>185</v>
@@ -3708,7 +3708,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="D11" t="n">
         <v>138</v>
@@ -3722,7 +3722,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D12" t="n">
         <v>94</v>
@@ -3736,7 +3736,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D13" t="n">
         <v>64</v>
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6197</v>
+        <v>6246</v>
       </c>
       <c r="C2" t="n">
-        <v>4078</v>
+        <v>7867</v>
       </c>
       <c r="D2" t="n">
-        <v>9160</v>
+        <v>13510</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2183</v>
+        <v>2615</v>
       </c>
       <c r="C2" t="n">
-        <v>6095</v>
+        <v>8271</v>
       </c>
       <c r="D2" t="n">
-        <v>15640</v>
+        <v>8204</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2560</v>
+        <v>3114</v>
       </c>
       <c r="C3" t="n">
-        <v>3888</v>
+        <v>7384</v>
       </c>
       <c r="D3" t="n">
-        <v>19647</v>
+        <v>11334</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3195</v>
+        <v>3586</v>
       </c>
       <c r="C4" t="n">
-        <v>5189</v>
+        <v>8603</v>
       </c>
       <c r="D4" t="n">
-        <v>17182</v>
+        <v>10828</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1408</v>
+        <v>1441</v>
       </c>
       <c r="C5" t="n">
-        <v>9438</v>
+        <v>11816</v>
       </c>
       <c r="D5" t="n">
-        <v>7910</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>470</v>
+        <v>493</v>
       </c>
       <c r="C6" t="n">
-        <v>6495</v>
+        <v>7241</v>
       </c>
       <c r="D6" t="n">
-        <v>2345</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="C7" t="n">
-        <v>2620</v>
+        <v>2898</v>
       </c>
       <c r="D7" t="n">
-        <v>563</v>
+        <v>543</v>
       </c>
     </row>
     <row r="8">
@@ -4288,10 +4288,10 @@
         <v>21</v>
       </c>
       <c r="C8" t="n">
-        <v>937</v>
+        <v>1127</v>
       </c>
       <c r="D8" t="n">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="9">
@@ -4302,7 +4302,7 @@
         <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>302</v>
+        <v>354</v>
       </c>
       <c r="D9" t="n">
         <v>181</v>
@@ -4316,7 +4316,7 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="D10" t="n">
         <v>135</v>
@@ -4330,7 +4330,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D11" t="n">
         <v>92</v>
@@ -4344,7 +4344,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D12" t="n">
         <v>62</v>
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D13" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6748</v>
+        <v>6977</v>
       </c>
       <c r="C2" t="n">
-        <v>5667</v>
+        <v>6950</v>
       </c>
       <c r="D2" t="n">
-        <v>11190</v>
+        <v>17976</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2633</v>
+        <v>2653</v>
       </c>
       <c r="C3" t="n">
-        <v>2055</v>
+        <v>3964</v>
       </c>
       <c r="D3" t="n">
-        <v>2178</v>
+        <v>2909</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>79</v>
       </c>
       <c r="C4" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D4" t="n">
         <v>1538</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C5" t="n">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C6" t="n">
         <v>459</v>
       </c>
       <c r="D6" t="n">
-        <v>808</v>
+        <v>816</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>350</v>
       </c>
       <c r="D7" t="n">
-        <v>546</v>
+        <v>538</v>
       </c>
     </row>
     <row r="8">
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4609</v>
+        <v>4636</v>
       </c>
       <c r="C2" t="n">
-        <v>5494</v>
+        <v>5367</v>
       </c>
       <c r="D2" t="n">
-        <v>27662</v>
+        <v>15404</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3852</v>
+        <v>3954</v>
       </c>
       <c r="C3" t="n">
-        <v>3560</v>
+        <v>4875</v>
       </c>
       <c r="D3" t="n">
-        <v>3531</v>
+        <v>5226</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1177</v>
+        <v>1187</v>
       </c>
       <c r="C4" t="n">
-        <v>1266</v>
+        <v>2367</v>
       </c>
       <c r="D4" t="n">
-        <v>1620</v>
+        <v>1767</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D5" t="n">
-        <v>1186</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C6" t="n">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="D6" t="n">
-        <v>864</v>
+        <v>859</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C7" t="n">
         <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>589</v>
+        <v>584</v>
       </c>
     </row>
     <row r="8">
@@ -4913,7 +4913,7 @@
         <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="9">
@@ -4921,10 +4921,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C9" t="n">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D9" t="n">
         <v>363</v>
@@ -4935,7 +4935,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C10" t="n">
         <v>192</v>
@@ -4949,10 +4949,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D11" t="n">
         <v>270</v>
@@ -4983,7 +4983,7 @@
         <v>103</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="14">
@@ -4997,7 +4997,7 @@
         <v>83</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="15">
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
         <v>74</v>
@@ -5025,7 +5025,7 @@
         <v>71</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -5036,10 +5036,10 @@
         <v>12</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="18">
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4642</v>
+        <v>4860</v>
       </c>
       <c r="C2" t="n">
-        <v>5351</v>
+        <v>4205</v>
       </c>
       <c r="D2" t="n">
-        <v>41917</v>
+        <v>17466</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3480</v>
+        <v>3535</v>
       </c>
       <c r="C3" t="n">
-        <v>3994</v>
+        <v>4452</v>
       </c>
       <c r="D3" t="n">
-        <v>7137</v>
+        <v>6478</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2129</v>
+        <v>2186</v>
       </c>
       <c r="C4" t="n">
-        <v>2538</v>
+        <v>3738</v>
       </c>
       <c r="D4" t="n">
-        <v>1937</v>
+        <v>2377</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>543</v>
+        <v>537</v>
       </c>
       <c r="C5" t="n">
-        <v>785</v>
+        <v>1389</v>
       </c>
       <c r="D5" t="n">
-        <v>1217</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C6" t="n">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D6" t="n">
-        <v>910</v>
+        <v>908</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="D7" t="n">
-        <v>625</v>
+        <v>626</v>
       </c>
     </row>
     <row r="8">
@@ -5224,7 +5224,7 @@
         <v>358</v>
       </c>
       <c r="D8" t="n">
-        <v>462</v>
+        <v>454</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C9" t="n">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="D9" t="n">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="10">
@@ -5246,7 +5246,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C10" t="n">
         <v>210</v>
@@ -5263,7 +5263,7 @@
         <v>46</v>
       </c>
       <c r="C11" t="n">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D11" t="n">
         <v>280</v>
@@ -5277,10 +5277,10 @@
         <v>31</v>
       </c>
       <c r="C12" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D12" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="13">
@@ -5305,10 +5305,10 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D15" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16">
@@ -5336,7 +5336,7 @@
         <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17">
@@ -5347,10 +5347,10 @@
         <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5375,7 +5375,7 @@
         <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D19" t="n">
         <v>41</v>
@@ -5406,7 +5406,7 @@
         <v>122</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6068</v>
+        <v>5266</v>
       </c>
       <c r="C2" t="n">
-        <v>6694</v>
+        <v>4553</v>
       </c>
       <c r="D2" t="n">
-        <v>43816</v>
+        <v>18138</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3316</v>
+        <v>3423</v>
       </c>
       <c r="C3" t="n">
-        <v>4084</v>
+        <v>3764</v>
       </c>
       <c r="D3" t="n">
-        <v>11921</v>
+        <v>7692</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2391</v>
+        <v>2439</v>
       </c>
       <c r="C4" t="n">
-        <v>3267</v>
+        <v>4044</v>
       </c>
       <c r="D4" t="n">
-        <v>2826</v>
+        <v>3052</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1097</v>
+        <v>1115</v>
       </c>
       <c r="C5" t="n">
-        <v>1669</v>
+        <v>2564</v>
       </c>
       <c r="D5" t="n">
-        <v>1292</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C6" t="n">
-        <v>544</v>
+        <v>852</v>
       </c>
       <c r="D6" t="n">
-        <v>950</v>
+        <v>955</v>
       </c>
     </row>
     <row r="7">
@@ -5518,10 +5518,10 @@
         <v>143</v>
       </c>
       <c r="C7" t="n">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D7" t="n">
-        <v>659</v>
+        <v>660</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C8" t="n">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="D8" t="n">
-        <v>484</v>
+        <v>478</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C9" t="n">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="D9" t="n">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="10">
@@ -5560,7 +5560,7 @@
         <v>70</v>
       </c>
       <c r="C10" t="n">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="D10" t="n">
         <v>346</v>
@@ -5571,10 +5571,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C11" t="n">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D11" t="n">
         <v>286</v>
@@ -5588,10 +5588,10 @@
         <v>33</v>
       </c>
       <c r="C12" t="n">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D12" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="13">
@@ -5619,7 +5619,7 @@
         <v>99</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -5633,7 +5633,7 @@
         <v>81</v>
       </c>
       <c r="D15" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="16">
@@ -5647,7 +5647,7 @@
         <v>73</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5672,7 +5672,7 @@
         <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
         <v>60</v>
@@ -5717,7 +5717,7 @@
         <v>137</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5727</v>
+        <v>5958</v>
       </c>
       <c r="C2" t="n">
-        <v>12752</v>
+        <v>7993</v>
       </c>
       <c r="D2" t="n">
-        <v>35502</v>
+        <v>27721</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3374</v>
+        <v>3139</v>
       </c>
       <c r="C3" t="n">
-        <v>4438</v>
+        <v>3413</v>
       </c>
       <c r="D3" t="n">
-        <v>14985</v>
+        <v>8221</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1760</v>
+        <v>1808</v>
       </c>
       <c r="C4" t="n">
-        <v>3045</v>
+        <v>3155</v>
       </c>
       <c r="D4" t="n">
-        <v>3843</v>
+        <v>3318</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>916</v>
+        <v>933</v>
       </c>
       <c r="C5" t="n">
-        <v>1814</v>
+        <v>2444</v>
       </c>
       <c r="D5" t="n">
-        <v>1219</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="C6" t="n">
-        <v>748</v>
+        <v>1155</v>
       </c>
       <c r="D6" t="n">
-        <v>767</v>
+        <v>784</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C7" t="n">
-        <v>284</v>
+        <v>379</v>
       </c>
       <c r="D7" t="n">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D8" t="n">
-        <v>364</v>
+        <v>360</v>
       </c>
     </row>
     <row r="9">
@@ -5860,7 +5860,7 @@
         <v>197</v>
       </c>
       <c r="D9" t="n">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="10">
@@ -5868,10 +5868,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C10" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D10" t="n">
         <v>237</v>
@@ -5896,10 +5896,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C12" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D12" t="n">
         <v>148</v>
@@ -5944,7 +5944,7 @@
         <v>45</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -5969,7 +5969,7 @@
         <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D17" t="n">
         <v>50</v>
@@ -6028,7 +6028,7 @@
         <v>75</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6334</v>
+        <v>5262</v>
       </c>
       <c r="C2" t="n">
-        <v>5724</v>
+        <v>6986</v>
       </c>
       <c r="D2" t="n">
-        <v>36074</v>
+        <v>25253</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3779</v>
+        <v>3783</v>
       </c>
       <c r="C3" t="n">
-        <v>8003</v>
+        <v>5271</v>
       </c>
       <c r="D3" t="n">
-        <v>17328</v>
+        <v>11034</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2258</v>
+        <v>2172</v>
       </c>
       <c r="C4" t="n">
-        <v>3824</v>
+        <v>3247</v>
       </c>
       <c r="D4" t="n">
-        <v>5935</v>
+        <v>4252</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1196</v>
+        <v>1216</v>
       </c>
       <c r="C5" t="n">
-        <v>2479</v>
+        <v>2816</v>
       </c>
       <c r="D5" t="n">
-        <v>1710</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>571</v>
+        <v>590</v>
       </c>
       <c r="C6" t="n">
-        <v>1352</v>
+        <v>1883</v>
       </c>
       <c r="D6" t="n">
-        <v>842</v>
+        <v>867</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C7" t="n">
-        <v>547</v>
+        <v>819</v>
       </c>
       <c r="D7" t="n">
-        <v>550</v>
+        <v>561</v>
       </c>
     </row>
     <row r="8">
@@ -6154,10 +6154,10 @@
         <v>70</v>
       </c>
       <c r="C8" t="n">
-        <v>256</v>
+        <v>308</v>
       </c>
       <c r="D8" t="n">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="9">
@@ -6168,10 +6168,10 @@
         <v>47</v>
       </c>
       <c r="C9" t="n">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D9" t="n">
-        <v>281</v>
+        <v>278</v>
       </c>
     </row>
     <row r="10">
@@ -6179,7 +6179,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C10" t="n">
         <v>174</v>
@@ -6196,7 +6196,7 @@
         <v>23</v>
       </c>
       <c r="C11" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D11" t="n">
         <v>199</v>
@@ -6221,10 +6221,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D13" t="n">
         <v>119</v>
@@ -6235,10 +6235,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
         <v>98</v>
@@ -6255,7 +6255,7 @@
         <v>50</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -6280,7 +6280,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D17" t="n">
         <v>51</v>
@@ -6339,7 +6339,7 @@
         <v>83</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5828</v>
+        <v>4581</v>
       </c>
       <c r="C2" t="n">
-        <v>6587</v>
+        <v>6218</v>
       </c>
       <c r="D2" t="n">
-        <v>42694</v>
+        <v>19468</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4124</v>
+        <v>3716</v>
       </c>
       <c r="C3" t="n">
-        <v>5851</v>
+        <v>5427</v>
       </c>
       <c r="D3" t="n">
-        <v>19079</v>
+        <v>12514</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2597</v>
+        <v>2573</v>
       </c>
       <c r="C4" t="n">
-        <v>6111</v>
+        <v>4294</v>
       </c>
       <c r="D4" t="n">
-        <v>7942</v>
+        <v>5384</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1500</v>
+        <v>1494</v>
       </c>
       <c r="C5" t="n">
-        <v>3163</v>
+        <v>2997</v>
       </c>
       <c r="D5" t="n">
-        <v>2412</v>
+        <v>2122</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>803</v>
+        <v>816</v>
       </c>
       <c r="C6" t="n">
-        <v>1931</v>
+        <v>2362</v>
       </c>
       <c r="D6" t="n">
-        <v>988</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>333</v>
+        <v>346</v>
       </c>
       <c r="C7" t="n">
-        <v>959</v>
+        <v>1381</v>
       </c>
       <c r="D7" t="n">
-        <v>595</v>
+        <v>603</v>
       </c>
     </row>
     <row r="8">
@@ -6465,10 +6465,10 @@
         <v>114</v>
       </c>
       <c r="C8" t="n">
-        <v>404</v>
+        <v>565</v>
       </c>
       <c r="D8" t="n">
-        <v>407</v>
+        <v>412</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C9" t="n">
-        <v>232</v>
+        <v>258</v>
       </c>
       <c r="D9" t="n">
-        <v>295</v>
+        <v>292</v>
       </c>
     </row>
     <row r="10">
@@ -6490,7 +6490,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C10" t="n">
         <v>191</v>
@@ -6507,7 +6507,7 @@
         <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D11" t="n">
         <v>203</v>
@@ -6521,10 +6521,10 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="13">
@@ -6538,7 +6538,7 @@
         <v>90</v>
       </c>
       <c r="D13" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14">
@@ -6563,10 +6563,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -6591,10 +6591,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -6608,7 +6608,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -6650,7 +6650,7 @@
         <v>91</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_population_iteration_52_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_52_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6042</v>
+        <v>965</v>
       </c>
       <c r="C2" t="n">
-        <v>15102</v>
+        <v>3239</v>
       </c>
       <c r="D2" t="n">
-        <v>28063</v>
+        <v>18744</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3395</v>
+        <v>1438</v>
       </c>
       <c r="C3" t="n">
-        <v>5080</v>
+        <v>7547</v>
       </c>
       <c r="D3" t="n">
-        <v>12690</v>
+        <v>18640</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2662</v>
+        <v>879</v>
       </c>
       <c r="C4" t="n">
-        <v>4761</v>
+        <v>7769</v>
       </c>
       <c r="D4" t="n">
-        <v>6520</v>
+        <v>7832</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1773</v>
+        <v>416</v>
       </c>
       <c r="C5" t="n">
-        <v>3607</v>
+        <v>4378</v>
       </c>
       <c r="D5" t="n">
-        <v>2600</v>
+        <v>2318</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1030</v>
+        <v>199</v>
       </c>
       <c r="C6" t="n">
-        <v>2653</v>
+        <v>1478</v>
       </c>
       <c r="D6" t="n">
-        <v>1182</v>
+        <v>758</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>508</v>
+        <v>97</v>
       </c>
       <c r="C7" t="n">
-        <v>1847</v>
+        <v>590</v>
       </c>
       <c r="D7" t="n">
-        <v>663</v>
+        <v>493</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>192</v>
+        <v>74</v>
       </c>
       <c r="C8" t="n">
-        <v>956</v>
+        <v>341</v>
       </c>
       <c r="D8" t="n">
-        <v>433</v>
+        <v>374</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="C9" t="n">
-        <v>399</v>
+        <v>286</v>
       </c>
       <c r="D9" t="n">
-        <v>307</v>
+        <v>314</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="C10" t="n">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="D10" t="n">
-        <v>243</v>
+        <v>270</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>212</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>128</v>
+        <v>111</v>
       </c>
       <c r="D12" t="n">
-        <v>158</v>
+        <v>174</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>98</v>
+        <v>77</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>138</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>89</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>142</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7717</v>
+        <v>672</v>
       </c>
       <c r="C2" t="n">
-        <v>18010</v>
+        <v>10019</v>
       </c>
       <c r="D2" t="n">
-        <v>28674</v>
+        <v>24062</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3707</v>
+        <v>1024</v>
       </c>
       <c r="C3" t="n">
-        <v>8551</v>
+        <v>4618</v>
       </c>
       <c r="D3" t="n">
-        <v>13927</v>
+        <v>17343</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2553</v>
+        <v>990</v>
       </c>
       <c r="C4" t="n">
-        <v>4818</v>
+        <v>7560</v>
       </c>
       <c r="D4" t="n">
-        <v>7266</v>
+        <v>9565</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1912</v>
+        <v>552</v>
       </c>
       <c r="C5" t="n">
-        <v>4040</v>
+        <v>6044</v>
       </c>
       <c r="D5" t="n">
-        <v>3160</v>
+        <v>3200</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1245</v>
+        <v>271</v>
       </c>
       <c r="C6" t="n">
-        <v>3066</v>
+        <v>2924</v>
       </c>
       <c r="D6" t="n">
-        <v>1372</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>657</v>
+        <v>127</v>
       </c>
       <c r="C7" t="n">
-        <v>2191</v>
+        <v>1021</v>
       </c>
       <c r="D7" t="n">
-        <v>737</v>
+        <v>529</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>287</v>
+        <v>77</v>
       </c>
       <c r="C8" t="n">
-        <v>1348</v>
+        <v>459</v>
       </c>
       <c r="D8" t="n">
-        <v>458</v>
+        <v>391</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>107</v>
+        <v>56</v>
       </c>
       <c r="C9" t="n">
-        <v>629</v>
+        <v>311</v>
       </c>
       <c r="D9" t="n">
-        <v>322</v>
+        <v>318</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="C10" t="n">
-        <v>292</v>
+        <v>244</v>
       </c>
       <c r="D10" t="n">
-        <v>246</v>
+        <v>275</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="D11" t="n">
-        <v>208</v>
+        <v>217</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="D12" t="n">
-        <v>162</v>
+        <v>176</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>107</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>141</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>94</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>95</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>77</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8821</v>
+        <v>356</v>
       </c>
       <c r="C2" t="n">
-        <v>12192</v>
+        <v>4198</v>
       </c>
       <c r="D2" t="n">
-        <v>26341</v>
+        <v>16378</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4365</v>
+        <v>889</v>
       </c>
       <c r="C3" t="n">
-        <v>11060</v>
+        <v>6507</v>
       </c>
       <c r="D3" t="n">
-        <v>14901</v>
+        <v>17705</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2570</v>
+        <v>1090</v>
       </c>
       <c r="C4" t="n">
-        <v>6320</v>
+        <v>6998</v>
       </c>
       <c r="D4" t="n">
-        <v>8068</v>
+        <v>10554</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1935</v>
+        <v>558</v>
       </c>
       <c r="C5" t="n">
-        <v>4292</v>
+        <v>7196</v>
       </c>
       <c r="D5" t="n">
-        <v>3624</v>
+        <v>3619</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1383</v>
+        <v>237</v>
       </c>
       <c r="C6" t="n">
-        <v>3410</v>
+        <v>3773</v>
       </c>
       <c r="D6" t="n">
-        <v>1611</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>803</v>
+        <v>71</v>
       </c>
       <c r="C7" t="n">
-        <v>2528</v>
+        <v>1018</v>
       </c>
       <c r="D7" t="n">
-        <v>809</v>
+        <v>560</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>386</v>
+        <v>51</v>
       </c>
       <c r="C8" t="n">
-        <v>1686</v>
+        <v>466</v>
       </c>
       <c r="D8" t="n">
-        <v>491</v>
+        <v>434</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>153</v>
+        <v>26</v>
       </c>
       <c r="C9" t="n">
-        <v>897</v>
+        <v>239</v>
       </c>
       <c r="D9" t="n">
-        <v>332</v>
+        <v>369</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>59</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>417</v>
+        <v>190</v>
       </c>
       <c r="D10" t="n">
-        <v>253</v>
+        <v>212</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>220</v>
+        <v>130</v>
       </c>
       <c r="D11" t="n">
-        <v>208</v>
+        <v>172</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="C12" t="n">
-        <v>155</v>
+        <v>86</v>
       </c>
       <c r="D12" t="n">
-        <v>165</v>
+        <v>138</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>118</v>
+        <v>67</v>
       </c>
       <c r="D13" t="n">
-        <v>127</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>90</v>
+        <v>62</v>
       </c>
       <c r="D14" t="n">
-        <v>102</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C17" t="n">
-        <v>42</v>
+        <v>93</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>111</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7995</v>
+        <v>361</v>
       </c>
       <c r="C2" t="n">
-        <v>8290</v>
+        <v>5005</v>
       </c>
       <c r="D2" t="n">
-        <v>21644</v>
+        <v>16645</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4978</v>
+        <v>559</v>
       </c>
       <c r="C3" t="n">
-        <v>14628</v>
+        <v>4720</v>
       </c>
       <c r="D3" t="n">
-        <v>16133</v>
+        <v>16426</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1787</v>
+        <v>882</v>
       </c>
       <c r="C4" t="n">
-        <v>7639</v>
+        <v>6665</v>
       </c>
       <c r="D4" t="n">
-        <v>7849</v>
+        <v>11468</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1277</v>
+        <v>706</v>
       </c>
       <c r="C5" t="n">
-        <v>3341</v>
+        <v>7018</v>
       </c>
       <c r="D5" t="n">
-        <v>2552</v>
+        <v>4640</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>741</v>
+        <v>333</v>
       </c>
       <c r="C6" t="n">
-        <v>2477</v>
+        <v>5349</v>
       </c>
       <c r="D6" t="n">
-        <v>792</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>356</v>
+        <v>114</v>
       </c>
       <c r="C7" t="n">
-        <v>1652</v>
+        <v>2252</v>
       </c>
       <c r="D7" t="n">
-        <v>481</v>
+        <v>616</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>141</v>
+        <v>55</v>
       </c>
       <c r="C8" t="n">
-        <v>879</v>
+        <v>701</v>
       </c>
       <c r="D8" t="n">
-        <v>325</v>
+        <v>449</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>54</v>
+        <v>30</v>
       </c>
       <c r="C9" t="n">
-        <v>408</v>
+        <v>326</v>
       </c>
       <c r="D9" t="n">
-        <v>247</v>
+        <v>379</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="C10" t="n">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="D10" t="n">
-        <v>203</v>
+        <v>224</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="C11" t="n">
         <v>151</v>
       </c>
       <c r="D11" t="n">
-        <v>161</v>
+        <v>179</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>115</v>
+        <v>98</v>
       </c>
       <c r="D12" t="n">
-        <v>124</v>
+        <v>142</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
+        <v>69</v>
+      </c>
+      <c r="D14" t="n">
         <v>68</v>
-      </c>
-      <c r="D14" t="n">
-        <v>77</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>64</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>41</v>
+        <v>90</v>
       </c>
       <c r="D16" t="n">
-        <v>49</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>101</v>
       </c>
       <c r="D17" t="n">
-        <v>38</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>111</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4816</v>
+        <v>276</v>
       </c>
       <c r="C2" t="n">
-        <v>3842</v>
+        <v>2581</v>
       </c>
       <c r="D2" t="n">
-        <v>14696</v>
+        <v>13653</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5357</v>
+        <v>425</v>
       </c>
       <c r="C3" t="n">
-        <v>10610</v>
+        <v>4358</v>
       </c>
       <c r="D3" t="n">
-        <v>15953</v>
+        <v>15667</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2583</v>
+        <v>715</v>
       </c>
       <c r="C4" t="n">
-        <v>11061</v>
+        <v>5822</v>
       </c>
       <c r="D4" t="n">
-        <v>9033</v>
+        <v>11943</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1395</v>
+        <v>744</v>
       </c>
       <c r="C5" t="n">
-        <v>5206</v>
+        <v>6995</v>
       </c>
       <c r="D5" t="n">
-        <v>3184</v>
+        <v>5440</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>886</v>
+        <v>410</v>
       </c>
       <c r="C6" t="n">
-        <v>2902</v>
+        <v>6214</v>
       </c>
       <c r="D6" t="n">
-        <v>974</v>
+        <v>1728</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>335</v>
+        <v>125</v>
       </c>
       <c r="C7" t="n">
-        <v>2023</v>
+        <v>3285</v>
       </c>
       <c r="D7" t="n">
-        <v>525</v>
+        <v>686</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>118</v>
+        <v>52</v>
       </c>
       <c r="C8" t="n">
-        <v>1130</v>
+        <v>1069</v>
       </c>
       <c r="D8" t="n">
-        <v>339</v>
+        <v>483</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="C9" t="n">
-        <v>465</v>
+        <v>415</v>
       </c>
       <c r="D9" t="n">
-        <v>256</v>
+        <v>379</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C10" t="n">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="D10" t="n">
-        <v>211</v>
+        <v>231</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>168</v>
+        <v>155</v>
       </c>
       <c r="D11" t="n">
-        <v>166</v>
+        <v>186</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="D12" t="n">
-        <v>131</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D13" t="n">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>40</v>
+        <v>88</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>33</v>
+        <v>98</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4932</v>
+        <v>976</v>
       </c>
       <c r="C2" t="n">
-        <v>5230</v>
+        <v>5384</v>
       </c>
       <c r="D2" t="n">
-        <v>11288</v>
+        <v>26808</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4349</v>
+        <v>307</v>
       </c>
       <c r="C3" t="n">
-        <v>6589</v>
+        <v>3166</v>
       </c>
       <c r="D3" t="n">
-        <v>14710</v>
+        <v>14340</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3213</v>
+        <v>522</v>
       </c>
       <c r="C4" t="n">
-        <v>10610</v>
+        <v>5012</v>
       </c>
       <c r="D4" t="n">
-        <v>9887</v>
+        <v>12187</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1683</v>
+        <v>678</v>
       </c>
       <c r="C5" t="n">
-        <v>7851</v>
+        <v>6320</v>
       </c>
       <c r="D5" t="n">
-        <v>3985</v>
+        <v>6273</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1020</v>
+        <v>498</v>
       </c>
       <c r="C6" t="n">
-        <v>3941</v>
+        <v>6553</v>
       </c>
       <c r="D6" t="n">
-        <v>1279</v>
+        <v>2239</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>481</v>
+        <v>203</v>
       </c>
       <c r="C7" t="n">
-        <v>2421</v>
+        <v>4489</v>
       </c>
       <c r="D7" t="n">
-        <v>581</v>
+        <v>821</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>172</v>
+        <v>69</v>
       </c>
       <c r="C8" t="n">
-        <v>1499</v>
+        <v>1947</v>
       </c>
       <c r="D8" t="n">
-        <v>359</v>
+        <v>503</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>57</v>
+        <v>31</v>
       </c>
       <c r="C9" t="n">
-        <v>717</v>
+        <v>656</v>
       </c>
       <c r="D9" t="n">
-        <v>263</v>
+        <v>391</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C10" t="n">
-        <v>317</v>
+        <v>294</v>
       </c>
       <c r="D10" t="n">
-        <v>215</v>
+        <v>243</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="D11" t="n">
-        <v>169</v>
+        <v>189</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="D12" t="n">
-        <v>133</v>
+        <v>139</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>95</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="D14" t="n">
-        <v>63</v>
+        <v>56</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>91</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>36</v>
+        <v>98</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2923</v>
+        <v>663</v>
       </c>
       <c r="C2" t="n">
-        <v>2438</v>
+        <v>2886</v>
       </c>
       <c r="D2" t="n">
-        <v>7895</v>
+        <v>19516</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4367</v>
+        <v>529</v>
       </c>
       <c r="C3" t="n">
-        <v>5932</v>
+        <v>4004</v>
       </c>
       <c r="D3" t="n">
-        <v>14024</v>
+        <v>16281</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3530</v>
+        <v>882</v>
       </c>
       <c r="C4" t="n">
-        <v>10095</v>
+        <v>6966</v>
       </c>
       <c r="D4" t="n">
-        <v>10515</v>
+        <v>12499</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1771</v>
+        <v>497</v>
       </c>
       <c r="C5" t="n">
-        <v>9632</v>
+        <v>9249</v>
       </c>
       <c r="D5" t="n">
-        <v>4209</v>
+        <v>5712</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>859</v>
+        <v>187</v>
       </c>
       <c r="C6" t="n">
-        <v>4790</v>
+        <v>5940</v>
       </c>
       <c r="D6" t="n">
-        <v>1257</v>
+        <v>1810</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>63</v>
       </c>
       <c r="C7" t="n">
-        <v>2603</v>
+        <v>1908</v>
       </c>
       <c r="D7" t="n">
-        <v>581</v>
+        <v>605</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>52</v>
+        <v>28</v>
       </c>
       <c r="C8" t="n">
-        <v>1158</v>
+        <v>642</v>
       </c>
       <c r="D8" t="n">
-        <v>377</v>
+        <v>383</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C9" t="n">
-        <v>310</v>
+        <v>288</v>
       </c>
       <c r="D9" t="n">
-        <v>288</v>
+        <v>238</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="D10" t="n">
-        <v>165</v>
+        <v>185</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="D11" t="n">
-        <v>130</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D12" t="n">
-        <v>97</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>54</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>43</v>
+        <v>89</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>35</v>
+        <v>96</v>
       </c>
       <c r="D15" t="n">
-        <v>35</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3528</v>
+        <v>347</v>
       </c>
       <c r="C2" t="n">
-        <v>9689</v>
+        <v>1853</v>
       </c>
       <c r="D2" t="n">
-        <v>10036</v>
+        <v>14012</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3228</v>
+        <v>489</v>
       </c>
       <c r="C3" t="n">
-        <v>3879</v>
+        <v>3095</v>
       </c>
       <c r="D3" t="n">
-        <v>12382</v>
+        <v>15733</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3405</v>
+        <v>601</v>
       </c>
       <c r="C4" t="n">
-        <v>8023</v>
+        <v>5156</v>
       </c>
       <c r="D4" t="n">
-        <v>10734</v>
+        <v>12200</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2181</v>
+        <v>467</v>
       </c>
       <c r="C5" t="n">
-        <v>9636</v>
+        <v>7268</v>
       </c>
       <c r="D5" t="n">
-        <v>4989</v>
+        <v>5914</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1086</v>
+        <v>179</v>
       </c>
       <c r="C6" t="n">
-        <v>6885</v>
+        <v>5991</v>
       </c>
       <c r="D6" t="n">
-        <v>1637</v>
+        <v>1975</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>329</v>
+        <v>50</v>
       </c>
       <c r="C7" t="n">
-        <v>3484</v>
+        <v>2583</v>
       </c>
       <c r="D7" t="n">
-        <v>666</v>
+        <v>600</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>71</v>
+        <v>14</v>
       </c>
       <c r="C8" t="n">
-        <v>1704</v>
+        <v>717</v>
       </c>
       <c r="D8" t="n">
-        <v>398</v>
+        <v>331</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>593</v>
+        <v>260</v>
       </c>
       <c r="D9" t="n">
-        <v>295</v>
+        <v>187</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>227</v>
+        <v>126</v>
       </c>
       <c r="D10" t="n">
-        <v>174</v>
+        <v>141</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>135</v>
+        <v>75</v>
       </c>
       <c r="D11" t="n">
-        <v>134</v>
+        <v>99</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>83</v>
+        <v>53</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2443</v>
+        <v>180</v>
       </c>
       <c r="C2" t="n">
-        <v>5046</v>
+        <v>4989</v>
       </c>
       <c r="D2" t="n">
-        <v>8398</v>
+        <v>22621</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2913</v>
+        <v>355</v>
       </c>
       <c r="C3" t="n">
-        <v>5570</v>
+        <v>2122</v>
       </c>
       <c r="D3" t="n">
-        <v>11545</v>
+        <v>14363</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3087</v>
+        <v>478</v>
       </c>
       <c r="C4" t="n">
-        <v>6416</v>
+        <v>3970</v>
       </c>
       <c r="D4" t="n">
-        <v>10716</v>
+        <v>12473</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2411</v>
+        <v>479</v>
       </c>
       <c r="C5" t="n">
-        <v>9232</v>
+        <v>6021</v>
       </c>
       <c r="D5" t="n">
-        <v>5491</v>
+        <v>6820</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1269</v>
+        <v>279</v>
       </c>
       <c r="C6" t="n">
-        <v>7995</v>
+        <v>6622</v>
       </c>
       <c r="D6" t="n">
-        <v>1955</v>
+        <v>2590</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>297</v>
+        <v>92</v>
       </c>
       <c r="C7" t="n">
-        <v>4521</v>
+        <v>4218</v>
       </c>
       <c r="D7" t="n">
-        <v>738</v>
+        <v>809</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>57</v>
+        <v>25</v>
       </c>
       <c r="C8" t="n">
-        <v>2144</v>
+        <v>1583</v>
       </c>
       <c r="D8" t="n">
-        <v>410</v>
+        <v>367</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C9" t="n">
-        <v>667</v>
+        <v>459</v>
       </c>
       <c r="D9" t="n">
-        <v>293</v>
+        <v>204</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>233</v>
+        <v>182</v>
       </c>
       <c r="D10" t="n">
-        <v>177</v>
+        <v>146</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>132</v>
+        <v>94</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>102</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="D12" t="n">
-        <v>92</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>9</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3616</v>
+        <v>153</v>
       </c>
       <c r="C2" t="n">
-        <v>14358</v>
+        <v>9009</v>
       </c>
       <c r="D2" t="n">
-        <v>11026</v>
+        <v>24188</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2316</v>
+        <v>234</v>
       </c>
       <c r="C3" t="n">
-        <v>4824</v>
+        <v>3053</v>
       </c>
       <c r="D3" t="n">
-        <v>10428</v>
+        <v>14563</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2630</v>
+        <v>370</v>
       </c>
       <c r="C4" t="n">
-        <v>5871</v>
+        <v>2964</v>
       </c>
       <c r="D4" t="n">
-        <v>10509</v>
+        <v>12420</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2427</v>
+        <v>432</v>
       </c>
       <c r="C5" t="n">
-        <v>7904</v>
+        <v>4911</v>
       </c>
       <c r="D5" t="n">
-        <v>6026</v>
+        <v>7535</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1512</v>
+        <v>336</v>
       </c>
       <c r="C6" t="n">
-        <v>8481</v>
+        <v>6278</v>
       </c>
       <c r="D6" t="n">
-        <v>2371</v>
+        <v>3179</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>534</v>
+        <v>152</v>
       </c>
       <c r="C7" t="n">
-        <v>5778</v>
+        <v>5258</v>
       </c>
       <c r="D7" t="n">
-        <v>873</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>110</v>
+        <v>45</v>
       </c>
       <c r="C8" t="n">
-        <v>2958</v>
+        <v>2744</v>
       </c>
       <c r="D8" t="n">
-        <v>441</v>
+        <v>428</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="C9" t="n">
-        <v>1150</v>
+        <v>932</v>
       </c>
       <c r="D9" t="n">
-        <v>301</v>
+        <v>222</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>362</v>
+        <v>293</v>
       </c>
       <c r="D10" t="n">
-        <v>185</v>
+        <v>152</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>161</v>
+        <v>127</v>
       </c>
       <c r="D11" t="n">
-        <v>138</v>
+        <v>106</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="D12" t="n">
-        <v>94</v>
+        <v>68</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>37</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>59</v>
+        <v>22</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>68</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6246</v>
+        <v>2782</v>
       </c>
       <c r="C2" t="n">
-        <v>7867</v>
+        <v>7173</v>
       </c>
       <c r="D2" t="n">
-        <v>13510</v>
+        <v>13625</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>843</v>
+        <v>855</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="C4" t="n">
-        <v>313</v>
+        <v>344</v>
       </c>
       <c r="D4" t="n">
-        <v>1805</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>249</v>
+        <v>314</v>
       </c>
       <c r="C5" t="n">
-        <v>515</v>
+        <v>586</v>
       </c>
       <c r="D5" t="n">
-        <v>1038</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>182</v>
+        <v>255</v>
       </c>
       <c r="C6" t="n">
-        <v>395</v>
+        <v>488</v>
       </c>
       <c r="D6" t="n">
-        <v>777</v>
+        <v>898</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>129</v>
+        <v>202</v>
       </c>
       <c r="C7" t="n">
-        <v>293</v>
+        <v>388</v>
       </c>
       <c r="D7" t="n">
-        <v>496</v>
+        <v>596</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>99</v>
+        <v>171</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>420</v>
+        <v>531</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>136</v>
       </c>
       <c r="C9" t="n">
-        <v>187</v>
+        <v>277</v>
       </c>
       <c r="D9" t="n">
-        <v>349</v>
+        <v>445</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>265</v>
       </c>
       <c r="D10" t="n">
-        <v>362</v>
+        <v>485</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="C11" t="n">
-        <v>137</v>
+        <v>215</v>
       </c>
       <c r="D11" t="n">
-        <v>245</v>
+        <v>327</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>169</v>
       </c>
       <c r="D12" t="n">
-        <v>196</v>
+        <v>274</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="C13" t="n">
-        <v>84</v>
+        <v>142</v>
       </c>
       <c r="D13" t="n">
-        <v>168</v>
+        <v>234</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>128</v>
       </c>
       <c r="D14" t="n">
-        <v>145</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>127</v>
       </c>
       <c r="D15" t="n">
-        <v>117</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>124</v>
       </c>
       <c r="D16" t="n">
-        <v>97</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="C17" t="n">
-        <v>66</v>
+        <v>119</v>
       </c>
       <c r="D17" t="n">
-        <v>76</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C18" t="n">
-        <v>63</v>
+        <v>116</v>
       </c>
       <c r="D18" t="n">
-        <v>57</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C19" t="n">
-        <v>60</v>
+        <v>111</v>
       </c>
       <c r="D19" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21">
@@ -4156,10 +4156,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C21" t="n">
-        <v>72</v>
+        <v>131</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2615</v>
+        <v>240</v>
       </c>
       <c r="C2" t="n">
-        <v>8271</v>
+        <v>11617</v>
       </c>
       <c r="D2" t="n">
-        <v>8204</v>
+        <v>23902</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3114</v>
+        <v>169</v>
       </c>
       <c r="C3" t="n">
-        <v>7384</v>
+        <v>4940</v>
       </c>
       <c r="D3" t="n">
-        <v>11334</v>
+        <v>14839</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3586</v>
+        <v>273</v>
       </c>
       <c r="C4" t="n">
-        <v>8603</v>
+        <v>2942</v>
       </c>
       <c r="D4" t="n">
-        <v>10828</v>
+        <v>12371</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1441</v>
+        <v>375</v>
       </c>
       <c r="C5" t="n">
-        <v>11816</v>
+        <v>3920</v>
       </c>
       <c r="D5" t="n">
-        <v>5500</v>
+        <v>7937</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>493</v>
+        <v>345</v>
       </c>
       <c r="C6" t="n">
-        <v>7241</v>
+        <v>5642</v>
       </c>
       <c r="D6" t="n">
-        <v>1906</v>
+        <v>3764</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>101</v>
+        <v>202</v>
       </c>
       <c r="C7" t="n">
-        <v>2898</v>
+        <v>5624</v>
       </c>
       <c r="D7" t="n">
-        <v>543</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>21</v>
+        <v>74</v>
       </c>
       <c r="C8" t="n">
-        <v>1127</v>
+        <v>3753</v>
       </c>
       <c r="D8" t="n">
-        <v>294</v>
+        <v>513</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="C9" t="n">
-        <v>354</v>
+        <v>1624</v>
       </c>
       <c r="D9" t="n">
-        <v>181</v>
+        <v>243</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>157</v>
+        <v>521</v>
       </c>
       <c r="D10" t="n">
-        <v>135</v>
+        <v>159</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>90</v>
+        <v>185</v>
       </c>
       <c r="D11" t="n">
-        <v>92</v>
+        <v>110</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="D12" t="n">
-        <v>62</v>
+        <v>70</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="D13" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>66</v>
+        <v>31</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6977</v>
+        <v>2457</v>
       </c>
       <c r="C2" t="n">
-        <v>6950</v>
+        <v>5679</v>
       </c>
       <c r="D2" t="n">
-        <v>17976</v>
+        <v>30715</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2653</v>
+        <v>921</v>
       </c>
       <c r="C3" t="n">
-        <v>3964</v>
+        <v>2832</v>
       </c>
       <c r="D3" t="n">
-        <v>2909</v>
+        <v>2472</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C4" t="n">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="D4" t="n">
-        <v>1538</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>193</v>
+        <v>148</v>
       </c>
       <c r="C5" t="n">
-        <v>381</v>
+        <v>334</v>
       </c>
       <c r="D5" t="n">
-        <v>1161</v>
+        <v>986</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>200</v>
+        <v>143</v>
       </c>
       <c r="C6" t="n">
-        <v>459</v>
+        <v>360</v>
       </c>
       <c r="D6" t="n">
-        <v>816</v>
+        <v>712</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>102</v>
       </c>
       <c r="C7" t="n">
-        <v>350</v>
+        <v>277</v>
       </c>
       <c r="D7" t="n">
-        <v>538</v>
+        <v>466</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>260</v>
+        <v>206</v>
       </c>
       <c r="D8" t="n">
-        <v>429</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="C9" t="n">
-        <v>205</v>
+        <v>169</v>
       </c>
       <c r="D9" t="n">
-        <v>354</v>
+        <v>313</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="C10" t="n">
-        <v>180</v>
+        <v>151</v>
       </c>
       <c r="D10" t="n">
-        <v>356</v>
+        <v>324</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>154</v>
+        <v>129</v>
       </c>
       <c r="D11" t="n">
-        <v>261</v>
+        <v>231</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>199</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D18" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>10</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C21" t="n">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4636</v>
+        <v>1791</v>
       </c>
       <c r="C2" t="n">
-        <v>5367</v>
+        <v>7674</v>
       </c>
       <c r="D2" t="n">
-        <v>15404</v>
+        <v>23566</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3954</v>
+        <v>1422</v>
       </c>
       <c r="C3" t="n">
-        <v>4875</v>
+        <v>3904</v>
       </c>
       <c r="D3" t="n">
-        <v>5226</v>
+        <v>7256</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1187</v>
+        <v>453</v>
       </c>
       <c r="C4" t="n">
-        <v>2367</v>
+        <v>1814</v>
       </c>
       <c r="D4" t="n">
-        <v>1767</v>
+        <v>1618</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C5" t="n">
-        <v>219</v>
+        <v>206</v>
       </c>
       <c r="D5" t="n">
-        <v>1198</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>185</v>
+        <v>135</v>
       </c>
       <c r="C6" t="n">
-        <v>410</v>
+        <v>343</v>
       </c>
       <c r="D6" t="n">
-        <v>859</v>
+        <v>747</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>114</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>324</v>
       </c>
       <c r="D7" t="n">
-        <v>584</v>
+        <v>509</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>83</v>
       </c>
       <c r="C8" t="n">
-        <v>307</v>
+        <v>244</v>
       </c>
       <c r="D8" t="n">
-        <v>439</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85</v>
+        <v>64</v>
       </c>
       <c r="C9" t="n">
-        <v>232</v>
+        <v>188</v>
       </c>
       <c r="D9" t="n">
-        <v>363</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>160</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>318</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>139</v>
       </c>
       <c r="D11" t="n">
-        <v>270</v>
+        <v>244</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C12" t="n">
-        <v>135</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>206</v>
+        <v>187</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>172</v>
+        <v>155</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C21" t="n">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4860</v>
+        <v>1785</v>
       </c>
       <c r="C2" t="n">
-        <v>4205</v>
+        <v>8169</v>
       </c>
       <c r="D2" t="n">
-        <v>17466</v>
+        <v>27080</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3535</v>
+        <v>1326</v>
       </c>
       <c r="C3" t="n">
-        <v>4452</v>
+        <v>5291</v>
       </c>
       <c r="D3" t="n">
-        <v>6478</v>
+        <v>9462</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2186</v>
+        <v>822</v>
       </c>
       <c r="C4" t="n">
-        <v>3738</v>
+        <v>3020</v>
       </c>
       <c r="D4" t="n">
-        <v>2377</v>
+        <v>2705</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>537</v>
+        <v>240</v>
       </c>
       <c r="C5" t="n">
-        <v>1389</v>
+        <v>1127</v>
       </c>
       <c r="D5" t="n">
-        <v>1253</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>148</v>
+        <v>111</v>
       </c>
       <c r="C6" t="n">
-        <v>304</v>
+        <v>262</v>
       </c>
       <c r="D6" t="n">
-        <v>908</v>
+        <v>794</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>116</v>
       </c>
       <c r="C7" t="n">
-        <v>405</v>
+        <v>334</v>
       </c>
       <c r="D7" t="n">
-        <v>626</v>
+        <v>548</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>125</v>
+        <v>91</v>
       </c>
       <c r="C8" t="n">
-        <v>358</v>
+        <v>286</v>
       </c>
       <c r="D8" t="n">
-        <v>454</v>
+        <v>407</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>90</v>
+        <v>67</v>
       </c>
       <c r="C9" t="n">
-        <v>268</v>
+        <v>216</v>
       </c>
       <c r="D9" t="n">
-        <v>371</v>
+        <v>329</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>173</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>314</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="C11" t="n">
-        <v>174</v>
+        <v>148</v>
       </c>
       <c r="D11" t="n">
-        <v>280</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C12" t="n">
-        <v>147</v>
+        <v>124</v>
       </c>
       <c r="D12" t="n">
-        <v>213</v>
+        <v>194</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>173</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C21" t="n">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5266</v>
+        <v>1831</v>
       </c>
       <c r="C2" t="n">
-        <v>4553</v>
+        <v>4946</v>
       </c>
       <c r="D2" t="n">
-        <v>18138</v>
+        <v>33799</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3423</v>
+        <v>1278</v>
       </c>
       <c r="C3" t="n">
-        <v>3764</v>
+        <v>5952</v>
       </c>
       <c r="D3" t="n">
-        <v>7692</v>
+        <v>11599</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2439</v>
+        <v>929</v>
       </c>
       <c r="C4" t="n">
-        <v>4044</v>
+        <v>4265</v>
       </c>
       <c r="D4" t="n">
-        <v>3052</v>
+        <v>3894</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1115</v>
+        <v>455</v>
       </c>
       <c r="C5" t="n">
-        <v>2564</v>
+        <v>2157</v>
       </c>
       <c r="D5" t="n">
-        <v>1397</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>297</v>
+        <v>158</v>
       </c>
       <c r="C6" t="n">
-        <v>852</v>
+        <v>723</v>
       </c>
       <c r="D6" t="n">
-        <v>955</v>
+        <v>841</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>143</v>
+        <v>107</v>
       </c>
       <c r="C7" t="n">
-        <v>354</v>
+        <v>295</v>
       </c>
       <c r="D7" t="n">
-        <v>660</v>
+        <v>580</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>130</v>
+        <v>95</v>
       </c>
       <c r="C8" t="n">
-        <v>376</v>
+        <v>310</v>
       </c>
       <c r="D8" t="n">
-        <v>478</v>
+        <v>427</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>96</v>
+        <v>71</v>
       </c>
       <c r="C9" t="n">
-        <v>310</v>
+        <v>250</v>
       </c>
       <c r="D9" t="n">
-        <v>376</v>
+        <v>338</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="C10" t="n">
-        <v>236</v>
+        <v>193</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>310</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="C11" t="n">
-        <v>187</v>
+        <v>159</v>
       </c>
       <c r="D11" t="n">
-        <v>286</v>
+        <v>257</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>158</v>
+        <v>134</v>
       </c>
       <c r="D12" t="n">
-        <v>217</v>
+        <v>200</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C13" t="n">
-        <v>128</v>
+        <v>108</v>
       </c>
       <c r="D13" t="n">
-        <v>176</v>
+        <v>159</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C16" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D16" t="n">
-        <v>101</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C21" t="n">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5958</v>
+        <v>1438</v>
       </c>
       <c r="C2" t="n">
-        <v>7993</v>
+        <v>5514</v>
       </c>
       <c r="D2" t="n">
-        <v>27721</v>
+        <v>37060</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3139</v>
+        <v>1265</v>
       </c>
       <c r="C3" t="n">
-        <v>3413</v>
+        <v>4769</v>
       </c>
       <c r="D3" t="n">
-        <v>8221</v>
+        <v>14156</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1808</v>
+        <v>947</v>
       </c>
       <c r="C4" t="n">
-        <v>3155</v>
+        <v>5042</v>
       </c>
       <c r="D4" t="n">
-        <v>3318</v>
+        <v>5143</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>933</v>
+        <v>591</v>
       </c>
       <c r="C5" t="n">
-        <v>2444</v>
+        <v>3225</v>
       </c>
       <c r="D5" t="n">
-        <v>1317</v>
+        <v>1801</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>331</v>
+        <v>269</v>
       </c>
       <c r="C6" t="n">
-        <v>1155</v>
+        <v>1444</v>
       </c>
       <c r="D6" t="n">
-        <v>784</v>
+        <v>923</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>95</v>
+        <v>119</v>
       </c>
       <c r="C7" t="n">
-        <v>379</v>
+        <v>508</v>
       </c>
       <c r="D7" t="n">
-        <v>514</v>
+        <v>611</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>94</v>
       </c>
       <c r="C8" t="n">
-        <v>223</v>
+        <v>302</v>
       </c>
       <c r="D8" t="n">
-        <v>360</v>
+        <v>448</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="C9" t="n">
-        <v>197</v>
+        <v>275</v>
       </c>
       <c r="D9" t="n">
-        <v>268</v>
+        <v>348</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="C10" t="n">
-        <v>152</v>
+        <v>218</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>307</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="C11" t="n">
-        <v>115</v>
+        <v>173</v>
       </c>
       <c r="D11" t="n">
-        <v>194</v>
+        <v>262</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>91</v>
+        <v>144</v>
       </c>
       <c r="D12" t="n">
-        <v>148</v>
+        <v>205</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>74</v>
+        <v>118</v>
       </c>
       <c r="D13" t="n">
-        <v>116</v>
+        <v>161</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>94</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C16" t="n">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6022,10 +6022,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>75</v>
+        <v>133</v>
       </c>
       <c r="D21" t="n">
         <v>5</v>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5262</v>
+        <v>1955</v>
       </c>
       <c r="C2" t="n">
-        <v>6986</v>
+        <v>13584</v>
       </c>
       <c r="D2" t="n">
-        <v>25253</v>
+        <v>34925</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3783</v>
+        <v>1109</v>
       </c>
       <c r="C3" t="n">
-        <v>5271</v>
+        <v>4489</v>
       </c>
       <c r="D3" t="n">
-        <v>11034</v>
+        <v>16480</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2172</v>
+        <v>934</v>
       </c>
       <c r="C4" t="n">
-        <v>3247</v>
+        <v>4798</v>
       </c>
       <c r="D4" t="n">
-        <v>4252</v>
+        <v>6544</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1216</v>
+        <v>669</v>
       </c>
       <c r="C5" t="n">
-        <v>2816</v>
+        <v>4016</v>
       </c>
       <c r="D5" t="n">
-        <v>1680</v>
+        <v>2274</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>590</v>
+        <v>373</v>
       </c>
       <c r="C6" t="n">
-        <v>1883</v>
+        <v>2283</v>
       </c>
       <c r="D6" t="n">
-        <v>867</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>193</v>
+        <v>167</v>
       </c>
       <c r="C7" t="n">
-        <v>819</v>
+        <v>948</v>
       </c>
       <c r="D7" t="n">
-        <v>561</v>
+        <v>647</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="C8" t="n">
-        <v>308</v>
+        <v>394</v>
       </c>
       <c r="D8" t="n">
-        <v>385</v>
+        <v>468</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>76</v>
       </c>
       <c r="C9" t="n">
-        <v>210</v>
+        <v>283</v>
       </c>
       <c r="D9" t="n">
-        <v>278</v>
+        <v>359</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="C10" t="n">
-        <v>174</v>
+        <v>241</v>
       </c>
       <c r="D10" t="n">
-        <v>240</v>
+        <v>306</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="C11" t="n">
-        <v>131</v>
+        <v>191</v>
       </c>
       <c r="D11" t="n">
-        <v>199</v>
+        <v>265</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="C12" t="n">
-        <v>102</v>
+        <v>153</v>
       </c>
       <c r="D12" t="n">
-        <v>152</v>
+        <v>208</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>81</v>
+        <v>127</v>
       </c>
       <c r="D13" t="n">
-        <v>119</v>
+        <v>164</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>64</v>
+        <v>102</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>137</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>81</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6333,10 +6333,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="C21" t="n">
-        <v>83</v>
+        <v>145</v>
       </c>
       <c r="D21" t="n">
         <v>6</v>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4581</v>
+        <v>1743</v>
       </c>
       <c r="C2" t="n">
-        <v>6218</v>
+        <v>8367</v>
       </c>
       <c r="D2" t="n">
-        <v>19468</v>
+        <v>27418</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3716</v>
+        <v>1561</v>
       </c>
       <c r="C3" t="n">
-        <v>5427</v>
+        <v>8421</v>
       </c>
       <c r="D3" t="n">
-        <v>12514</v>
+        <v>18164</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2573</v>
+        <v>618</v>
       </c>
       <c r="C4" t="n">
-        <v>4294</v>
+        <v>6849</v>
       </c>
       <c r="D4" t="n">
-        <v>5384</v>
+        <v>5966</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1494</v>
+        <v>344</v>
       </c>
       <c r="C5" t="n">
-        <v>2997</v>
+        <v>2237</v>
       </c>
       <c r="D5" t="n">
-        <v>2122</v>
+        <v>1708</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>816</v>
+        <v>154</v>
       </c>
       <c r="C6" t="n">
-        <v>2362</v>
+        <v>929</v>
       </c>
       <c r="D6" t="n">
-        <v>1003</v>
+        <v>634</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>346</v>
+        <v>88</v>
       </c>
       <c r="C7" t="n">
-        <v>1381</v>
+        <v>386</v>
       </c>
       <c r="D7" t="n">
-        <v>603</v>
+        <v>458</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>114</v>
+        <v>70</v>
       </c>
       <c r="C8" t="n">
-        <v>565</v>
+        <v>277</v>
       </c>
       <c r="D8" t="n">
-        <v>412</v>
+        <v>351</v>
       </c>
     </row>
     <row r="9">
@@ -6479,10 +6479,10 @@
         <v>53</v>
       </c>
       <c r="C9" t="n">
-        <v>258</v>
+        <v>236</v>
       </c>
       <c r="D9" t="n">
-        <v>292</v>
+        <v>299</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="D10" t="n">
-        <v>241</v>
+        <v>259</v>
       </c>
     </row>
     <row r="11">
@@ -6504,10 +6504,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
         <v>203</v>
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="D12" t="n">
-        <v>155</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="D13" t="n">
-        <v>122</v>
+        <v>134</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C14" t="n">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>111</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18">
@@ -6602,13 +6602,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>145</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
